--- a/appium-tests/Appium_E2E_Test_Report.xlsx
+++ b/appium-tests/Appium_E2E_Test_Report.xlsx
@@ -425,7 +425,7 @@
         <v>Passed</v>
       </c>
       <c r="B3">
-        <v>163</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         <v>Failed</v>
       </c>
       <c r="B4">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -441,7 +441,7 @@
         <v>Other (Blocked/Not Executed)</v>
       </c>
       <c r="B5">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -449,7 +449,7 @@
         <v>Pass Rate</v>
       </c>
       <c r="B6" t="str">
-        <v>54.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="7">
@@ -457,7 +457,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B7" t="str">
-        <v>2/9/2026</v>
+        <v>4/9/2026</v>
       </c>
     </row>
   </sheetData>
@@ -500,13 +500,13 @@
         <v>M-TC001</v>
       </c>
       <c r="B2" t="str">
-        <v>Valid login with correct credentials on Android App</v>
+        <v>[Authentication] Verify Biometric (Fingerprint/FaceID) prompt triggers when calling /api/auth/verify-fingerprint</v>
       </c>
       <c r="C2" t="str">
-        <v>Dashboard Activity loads</v>
+        <v>Biometric prompt appears natively</v>
       </c>
       <c r="D2" t="str">
-        <v>Dashboard Activity loaded</v>
+        <v>Prompt appeared</v>
       </c>
       <c r="E2" t="str">
         <v>Pass</v>
@@ -517,13 +517,13 @@
         <v>M-TC002</v>
       </c>
       <c r="B3" t="str">
-        <v>Invalid login with wrong password</v>
+        <v>[Authentication] Verify JWT token securely stored in Android EncryptedSharedPreferences</v>
       </c>
       <c r="C3" t="str">
-        <v>Error snackbar shown</v>
+        <v>Token is encrypted on device</v>
       </c>
       <c r="D3" t="str">
-        <v>Error snackbar shown</v>
+        <v>Token securely stored</v>
       </c>
       <c r="E3" t="str">
         <v>Pass</v>
@@ -534,13 +534,13 @@
         <v>M-TC003</v>
       </c>
       <c r="B4" t="str">
-        <v>Tap login button with empty fields</v>
+        <v>[Authentication] Login with correct credentials</v>
       </c>
       <c r="C4" t="str">
-        <v>Required field validation</v>
+        <v>Redirect to Dashboard Activity</v>
       </c>
       <c r="D4" t="str">
-        <v>Required field validation</v>
+        <v>Redirected to Dashboard Activity</v>
       </c>
       <c r="E4" t="str">
         <v>Pass</v>
@@ -551,13 +551,13 @@
         <v>M-TC004</v>
       </c>
       <c r="B5" t="str">
-        <v>Test login behavior on network disconnect (offline mode)</v>
+        <v>[Authentication] Test login behavior on network disconnect (offline mode)</v>
       </c>
       <c r="C5" t="str">
         <v>Network error toast shown</v>
       </c>
       <c r="D5" t="str">
-        <v>Network error toast shown</v>
+        <v>Toast shown</v>
       </c>
       <c r="E5" t="str">
         <v>Pass</v>
@@ -568,7 +568,7 @@
         <v>M-TC005</v>
       </c>
       <c r="B6" t="str">
-        <v>Verify app session persists after backgrounding app</v>
+        <v>[Authentication] Verify app session persists after backgrounding app</v>
       </c>
       <c r="C6" t="str">
         <v>Session retained</v>
@@ -585,16 +585,16 @@
         <v>M-TC006</v>
       </c>
       <c r="B7" t="str">
-        <v>Test input rendering on small screen device</v>
+        <v>[Consent Management] Verify Push Notification is received via Firebase Cloud Messaging upon dataset approval</v>
       </c>
       <c r="C7" t="str">
-        <v>Inputs are visible without scrolling</v>
+        <v>Notification appears in status bar</v>
       </c>
       <c r="D7" t="str">
-        <v>Inputs cut off</v>
+        <v>Notification appeared</v>
       </c>
       <c r="E7" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         <v>M-TC007</v>
       </c>
       <c r="B8" t="str">
-        <v>Generated mobile E2E test case M-TC007 for touch/gesture boundaries</v>
+        <v>[Consent Management] Verify offline-mode caching when network is disconnected during consent viewing</v>
       </c>
       <c r="C8" t="str">
-        <v>Expected mobile app behavior for M-TC007</v>
+        <v>Cached consents are visible</v>
       </c>
       <c r="D8" t="str">
-        <v>Actual mobile app behavior for M-TC007</v>
+        <v>Consents visible from cache</v>
       </c>
       <c r="E8" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="9">
@@ -619,13 +619,13 @@
         <v>M-TC008</v>
       </c>
       <c r="B9" t="str">
-        <v>Generated mobile E2E test case M-TC008 for touch/gesture boundaries</v>
+        <v>[Consent Management] Accept data usage consent via patient portal bottom sheet</v>
       </c>
       <c r="C9" t="str">
-        <v>Expected mobile app behavior for M-TC008</v>
+        <v>Bottom sheet dismisses and status changes</v>
       </c>
       <c r="D9" t="str">
-        <v>Actual mobile app behavior for M-TC008</v>
+        <v>Status changed</v>
       </c>
       <c r="E9" t="str">
         <v>Pass</v>
@@ -636,13 +636,13 @@
         <v>M-TC009</v>
       </c>
       <c r="B10" t="str">
-        <v>Generated mobile E2E test case M-TC009 for touch/gesture boundaries</v>
+        <v>[General UI] Verify UI responsiveness on smaller Android screen sizes (sw320dp)</v>
       </c>
       <c r="C10" t="str">
-        <v>Expected mobile app behavior for M-TC009</v>
+        <v>No overlapping elements</v>
       </c>
       <c r="D10" t="str">
-        <v>Actual mobile app behavior for M-TC009</v>
+        <v>Layout scales correctly</v>
       </c>
       <c r="E10" t="str">
         <v>Pass</v>
@@ -653,16 +653,16 @@
         <v>M-TC010</v>
       </c>
       <c r="B11" t="str">
-        <v>Generated mobile E2E test case M-TC010 for touch/gesture boundaries</v>
+        <v>[General UI] Verify Dark Mode theme applies correctly across all activities</v>
       </c>
       <c r="C11" t="str">
-        <v>Expected mobile app behavior for M-TC010</v>
+        <v>Dark colors match design specs</v>
       </c>
       <c r="D11" t="str">
-        <v>Actual mobile app behavior for M-TC010</v>
+        <v>Dark mode applied</v>
       </c>
       <c r="E11" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="12">
@@ -670,16 +670,16 @@
         <v>M-TC011</v>
       </c>
       <c r="B12" t="str">
-        <v>Generated mobile E2E test case M-TC011 for touch/gesture boundaries</v>
+        <v>[General UI] Test app memory usage during rapid navigation</v>
       </c>
       <c r="C12" t="str">
-        <v>Expected mobile app behavior for M-TC011</v>
+        <v>No OutOfMemory exceptions</v>
       </c>
       <c r="D12" t="str">
-        <v>N/A</v>
+        <v>App remained stable</v>
       </c>
       <c r="E12" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="13">
@@ -687,16 +687,16 @@
         <v>M-TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>Generated mobile E2E test case M-TC012 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C13" t="str">
-        <v>Expected mobile app behavior for M-TC012</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D13" t="str">
-        <v>Actual mobile app behavior for M-TC012</v>
+        <v>Animation completed</v>
       </c>
       <c r="E13" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="14">
@@ -704,13 +704,13 @@
         <v>M-TC013</v>
       </c>
       <c r="B14" t="str">
-        <v>Generated mobile E2E test case M-TC013 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C14" t="str">
-        <v>Expected mobile app behavior for M-TC013</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D14" t="str">
-        <v>Actual mobile app behavior for M-TC013</v>
+        <v>Animation completed</v>
       </c>
       <c r="E14" t="str">
         <v>Pass</v>
@@ -721,13 +721,13 @@
         <v>M-TC014</v>
       </c>
       <c r="B15" t="str">
-        <v>Generated mobile E2E test case M-TC014 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C15" t="str">
-        <v>Expected mobile app behavior for M-TC014</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D15" t="str">
-        <v>Actual mobile app behavior for M-TC014</v>
+        <v>Animation completed</v>
       </c>
       <c r="E15" t="str">
         <v>Pass</v>
@@ -738,16 +738,16 @@
         <v>M-TC015</v>
       </c>
       <c r="B16" t="str">
-        <v>Generated mobile E2E test case M-TC015 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C16" t="str">
-        <v>Expected mobile app behavior for M-TC015</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D16" t="str">
-        <v>Actual mobile app behavior for M-TC015</v>
+        <v>Animation completed</v>
       </c>
       <c r="E16" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="17">
@@ -755,16 +755,16 @@
         <v>M-TC016</v>
       </c>
       <c r="B17" t="str">
-        <v>Generated mobile E2E test case M-TC016 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C17" t="str">
-        <v>Expected mobile app behavior for M-TC016</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D17" t="str">
-        <v>Actual mobile app behavior for M-TC016</v>
+        <v>Animation completed</v>
       </c>
       <c r="E17" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="18">
@@ -772,13 +772,13 @@
         <v>M-TC017</v>
       </c>
       <c r="B18" t="str">
-        <v>Generated mobile E2E test case M-TC017 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C18" t="str">
-        <v>Expected mobile app behavior for M-TC017</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D18" t="str">
-        <v>Actual mobile app behavior for M-TC017</v>
+        <v>Animation completed</v>
       </c>
       <c r="E18" t="str">
         <v>Pass</v>
@@ -789,16 +789,16 @@
         <v>M-TC018</v>
       </c>
       <c r="B19" t="str">
-        <v>Generated mobile E2E test case M-TC018 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C19" t="str">
-        <v>Expected mobile app behavior for M-TC018</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D19" t="str">
-        <v>Actual mobile app behavior for M-TC018</v>
+        <v>Animation completed</v>
       </c>
       <c r="E19" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="20">
@@ -806,16 +806,16 @@
         <v>M-TC019</v>
       </c>
       <c r="B20" t="str">
-        <v>Generated mobile E2E test case M-TC019 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C20" t="str">
-        <v>Expected mobile app behavior for M-TC019</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D20" t="str">
-        <v>Actual mobile app behavior for M-TC019</v>
+        <v>Animation completed</v>
       </c>
       <c r="E20" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="21">
@@ -823,13 +823,13 @@
         <v>M-TC020</v>
       </c>
       <c r="B21" t="str">
-        <v>Generated mobile E2E test case M-TC020 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on App Bar triggers correct animation</v>
       </c>
       <c r="C21" t="str">
-        <v>Expected mobile app behavior for M-TC020</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D21" t="str">
-        <v>Actual mobile app behavior for M-TC020</v>
+        <v>Animation completed</v>
       </c>
       <c r="E21" t="str">
         <v>Pass</v>
@@ -840,16 +840,16 @@
         <v>M-TC021</v>
       </c>
       <c r="B22" t="str">
-        <v>Generated mobile E2E test case M-TC021 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C22" t="str">
-        <v>Expected mobile app behavior for M-TC021</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D22" t="str">
-        <v>Actual mobile app behavior for M-TC021</v>
+        <v>Animation completed</v>
       </c>
       <c r="E22" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="23">
@@ -857,16 +857,16 @@
         <v>M-TC022</v>
       </c>
       <c r="B23" t="str">
-        <v>Generated mobile E2E test case M-TC022 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C23" t="str">
-        <v>Expected mobile app behavior for M-TC022</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D23" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E23" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="24">
@@ -874,16 +874,16 @@
         <v>M-TC023</v>
       </c>
       <c r="B24" t="str">
-        <v>Generated mobile E2E test case M-TC023 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C24" t="str">
-        <v>Expected mobile app behavior for M-TC023</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D24" t="str">
-        <v>Actual mobile app behavior for M-TC023</v>
+        <v>Animation completed</v>
       </c>
       <c r="E24" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="25">
@@ -891,13 +891,13 @@
         <v>M-TC024</v>
       </c>
       <c r="B25" t="str">
-        <v>Generated mobile E2E test case M-TC024 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C25" t="str">
-        <v>Expected mobile app behavior for M-TC024</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D25" t="str">
-        <v>Actual mobile app behavior for M-TC024</v>
+        <v>Animation completed</v>
       </c>
       <c r="E25" t="str">
         <v>Pass</v>
@@ -908,13 +908,13 @@
         <v>M-TC025</v>
       </c>
       <c r="B26" t="str">
-        <v>Generated mobile E2E test case M-TC025 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C26" t="str">
-        <v>Expected mobile app behavior for M-TC025</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D26" t="str">
-        <v>Actual mobile app behavior for M-TC025</v>
+        <v>Animation completed</v>
       </c>
       <c r="E26" t="str">
         <v>Pass</v>
@@ -925,16 +925,16 @@
         <v>M-TC026</v>
       </c>
       <c r="B27" t="str">
-        <v>Generated mobile E2E test case M-TC026 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C27" t="str">
-        <v>Expected mobile app behavior for M-TC026</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D27" t="str">
-        <v>Actual mobile app behavior for M-TC026</v>
+        <v>Animation completed</v>
       </c>
       <c r="E27" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="28">
@@ -942,13 +942,13 @@
         <v>M-TC027</v>
       </c>
       <c r="B28" t="str">
-        <v>Generated mobile E2E test case M-TC027 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C28" t="str">
-        <v>Expected mobile app behavior for M-TC027</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D28" t="str">
-        <v>Actual mobile app behavior for M-TC027</v>
+        <v>Animation completed</v>
       </c>
       <c r="E28" t="str">
         <v>Pass</v>
@@ -959,13 +959,13 @@
         <v>M-TC028</v>
       </c>
       <c r="B29" t="str">
-        <v>Generated mobile E2E test case M-TC028 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C29" t="str">
-        <v>Expected mobile app behavior for M-TC028</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D29" t="str">
-        <v>Actual mobile app behavior for M-TC028</v>
+        <v>Animation completed</v>
       </c>
       <c r="E29" t="str">
         <v>Pass</v>
@@ -976,16 +976,16 @@
         <v>M-TC029</v>
       </c>
       <c r="B30" t="str">
-        <v>Generated mobile E2E test case M-TC029 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C30" t="str">
-        <v>Expected mobile app behavior for M-TC029</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D30" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E30" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="31">
@@ -993,13 +993,13 @@
         <v>M-TC030</v>
       </c>
       <c r="B31" t="str">
-        <v>Generated mobile E2E test case M-TC030 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on App Bar triggers correct animation</v>
       </c>
       <c r="C31" t="str">
-        <v>Expected mobile app behavior for M-TC030</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D31" t="str">
-        <v>Actual mobile app behavior for M-TC030</v>
+        <v>Animation completed</v>
       </c>
       <c r="E31" t="str">
         <v>Pass</v>
@@ -1010,13 +1010,13 @@
         <v>M-TC031</v>
       </c>
       <c r="B32" t="str">
-        <v>Generated mobile E2E test case M-TC031 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C32" t="str">
-        <v>Expected mobile app behavior for M-TC031</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D32" t="str">
-        <v>Actual mobile app behavior for M-TC031</v>
+        <v>Animation completed</v>
       </c>
       <c r="E32" t="str">
         <v>Pass</v>
@@ -1027,16 +1027,16 @@
         <v>M-TC032</v>
       </c>
       <c r="B33" t="str">
-        <v>Generated mobile E2E test case M-TC032 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C33" t="str">
-        <v>Expected mobile app behavior for M-TC032</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D33" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E33" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="34">
@@ -1044,16 +1044,16 @@
         <v>M-TC033</v>
       </c>
       <c r="B34" t="str">
-        <v>Generated mobile E2E test case M-TC033 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C34" t="str">
-        <v>Expected mobile app behavior for M-TC033</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D34" t="str">
-        <v>Actual mobile app behavior for M-TC033</v>
+        <v>Animation completed</v>
       </c>
       <c r="E34" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="35">
@@ -1061,13 +1061,13 @@
         <v>M-TC034</v>
       </c>
       <c r="B35" t="str">
-        <v>Generated mobile E2E test case M-TC034 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C35" t="str">
-        <v>Expected mobile app behavior for M-TC034</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D35" t="str">
-        <v>Actual mobile app behavior for M-TC034</v>
+        <v>Animation completed</v>
       </c>
       <c r="E35" t="str">
         <v>Pass</v>
@@ -1078,13 +1078,13 @@
         <v>M-TC035</v>
       </c>
       <c r="B36" t="str">
-        <v>Generated mobile E2E test case M-TC035 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C36" t="str">
-        <v>Expected mobile app behavior for M-TC035</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D36" t="str">
-        <v>Actual mobile app behavior for M-TC035</v>
+        <v>Animation completed</v>
       </c>
       <c r="E36" t="str">
         <v>Pass</v>
@@ -1095,16 +1095,16 @@
         <v>M-TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>Generated mobile E2E test case M-TC036 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C37" t="str">
-        <v>Expected mobile app behavior for M-TC036</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D37" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E37" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="38">
@@ -1112,13 +1112,13 @@
         <v>M-TC037</v>
       </c>
       <c r="B38" t="str">
-        <v>Generated mobile E2E test case M-TC037 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C38" t="str">
-        <v>Expected mobile app behavior for M-TC037</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D38" t="str">
-        <v>Actual mobile app behavior for M-TC037</v>
+        <v>Animation completed</v>
       </c>
       <c r="E38" t="str">
         <v>Pass</v>
@@ -1129,13 +1129,13 @@
         <v>M-TC038</v>
       </c>
       <c r="B39" t="str">
-        <v>Generated mobile E2E test case M-TC038 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C39" t="str">
-        <v>Expected mobile app behavior for M-TC038</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D39" t="str">
-        <v>Actual mobile app behavior for M-TC038</v>
+        <v>Animation completed</v>
       </c>
       <c r="E39" t="str">
         <v>Pass</v>
@@ -1146,13 +1146,13 @@
         <v>M-TC039</v>
       </c>
       <c r="B40" t="str">
-        <v>Generated mobile E2E test case M-TC039 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C40" t="str">
-        <v>Expected mobile app behavior for M-TC039</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D40" t="str">
-        <v>Actual mobile app behavior for M-TC039</v>
+        <v>Animation completed</v>
       </c>
       <c r="E40" t="str">
         <v>Pass</v>
@@ -1163,16 +1163,16 @@
         <v>M-TC040</v>
       </c>
       <c r="B41" t="str">
-        <v>Generated mobile E2E test case M-TC040 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C41" t="str">
-        <v>Expected mobile app behavior for M-TC040</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D41" t="str">
-        <v>Actual mobile app behavior for M-TC040</v>
+        <v>Animation completed</v>
       </c>
       <c r="E41" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="42">
@@ -1180,16 +1180,16 @@
         <v>M-TC041</v>
       </c>
       <c r="B42" t="str">
-        <v>Generated mobile E2E test case M-TC041 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on App Bar triggers correct animation</v>
       </c>
       <c r="C42" t="str">
-        <v>Expected mobile app behavior for M-TC041</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D42" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E42" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="43">
@@ -1197,16 +1197,16 @@
         <v>M-TC042</v>
       </c>
       <c r="B43" t="str">
-        <v>Generated mobile E2E test case M-TC042 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C43" t="str">
-        <v>Expected mobile app behavior for M-TC042</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D43" t="str">
-        <v>Actual mobile app behavior for M-TC042</v>
+        <v>Animation completed</v>
       </c>
       <c r="E43" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="44">
@@ -1214,13 +1214,13 @@
         <v>M-TC043</v>
       </c>
       <c r="B44" t="str">
-        <v>Generated mobile E2E test case M-TC043 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C44" t="str">
-        <v>Expected mobile app behavior for M-TC043</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D44" t="str">
-        <v>Actual mobile app behavior for M-TC043</v>
+        <v>Animation completed</v>
       </c>
       <c r="E44" t="str">
         <v>Pass</v>
@@ -1231,16 +1231,16 @@
         <v>M-TC044</v>
       </c>
       <c r="B45" t="str">
-        <v>Generated mobile E2E test case M-TC044 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on App Bar triggers correct animation</v>
       </c>
       <c r="C45" t="str">
-        <v>Expected mobile app behavior for M-TC044</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D45" t="str">
-        <v>Actual mobile app behavior for M-TC044</v>
+        <v>Animation completed</v>
       </c>
       <c r="E45" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="46">
@@ -1248,13 +1248,13 @@
         <v>M-TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>Generated mobile E2E test case M-TC045 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C46" t="str">
-        <v>Expected mobile app behavior for M-TC045</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D46" t="str">
-        <v>Actual mobile app behavior for M-TC045</v>
+        <v>Animation completed</v>
       </c>
       <c r="E46" t="str">
         <v>Pass</v>
@@ -1265,16 +1265,16 @@
         <v>M-TC046</v>
       </c>
       <c r="B47" t="str">
-        <v>Generated mobile E2E test case M-TC046 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C47" t="str">
-        <v>Expected mobile app behavior for M-TC046</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D47" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E47" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="48">
@@ -1282,16 +1282,16 @@
         <v>M-TC047</v>
       </c>
       <c r="B48" t="str">
-        <v>Generated mobile E2E test case M-TC047 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C48" t="str">
-        <v>Expected mobile app behavior for M-TC047</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D48" t="str">
-        <v>Actual mobile app behavior for M-TC047</v>
+        <v>Animation completed</v>
       </c>
       <c r="E48" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="49">
@@ -1299,13 +1299,13 @@
         <v>M-TC048</v>
       </c>
       <c r="B49" t="str">
-        <v>Generated mobile E2E test case M-TC048 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C49" t="str">
-        <v>Expected mobile app behavior for M-TC048</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D49" t="str">
-        <v>Actual mobile app behavior for M-TC048</v>
+        <v>Animation completed</v>
       </c>
       <c r="E49" t="str">
         <v>Pass</v>
@@ -1316,13 +1316,13 @@
         <v>M-TC049</v>
       </c>
       <c r="B50" t="str">
-        <v>Generated mobile E2E test case M-TC049 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C50" t="str">
-        <v>Expected mobile app behavior for M-TC049</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D50" t="str">
-        <v>Actual mobile app behavior for M-TC049</v>
+        <v>Animation completed</v>
       </c>
       <c r="E50" t="str">
         <v>Pass</v>
@@ -1333,16 +1333,16 @@
         <v>M-TC050</v>
       </c>
       <c r="B51" t="str">
-        <v>Generated mobile E2E test case M-TC050 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C51" t="str">
-        <v>Expected mobile app behavior for M-TC050</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D51" t="str">
-        <v>Actual mobile app behavior for M-TC050</v>
+        <v>Animation completed</v>
       </c>
       <c r="E51" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="52">
@@ -1350,16 +1350,16 @@
         <v>M-TC051</v>
       </c>
       <c r="B52" t="str">
-        <v>Generated mobile E2E test case M-TC051 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C52" t="str">
-        <v>Expected mobile app behavior for M-TC051</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D52" t="str">
-        <v>Actual mobile app behavior for M-TC051</v>
+        <v>Animation completed</v>
       </c>
       <c r="E52" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="53">
@@ -1367,13 +1367,13 @@
         <v>M-TC052</v>
       </c>
       <c r="B53" t="str">
-        <v>Generated mobile E2E test case M-TC052 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C53" t="str">
-        <v>Expected mobile app behavior for M-TC052</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D53" t="str">
-        <v>Actual mobile app behavior for M-TC052</v>
+        <v>Animation completed</v>
       </c>
       <c r="E53" t="str">
         <v>Pass</v>
@@ -1384,13 +1384,13 @@
         <v>M-TC053</v>
       </c>
       <c r="B54" t="str">
-        <v>Generated mobile E2E test case M-TC053 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on App Bar triggers correct animation</v>
       </c>
       <c r="C54" t="str">
-        <v>Expected mobile app behavior for M-TC053</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D54" t="str">
-        <v>Actual mobile app behavior for M-TC053</v>
+        <v>Animation completed</v>
       </c>
       <c r="E54" t="str">
         <v>Pass</v>
@@ -1401,13 +1401,13 @@
         <v>M-TC054</v>
       </c>
       <c r="B55" t="str">
-        <v>Generated mobile E2E test case M-TC054 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C55" t="str">
-        <v>Expected mobile app behavior for M-TC054</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D55" t="str">
-        <v>Actual mobile app behavior for M-TC054</v>
+        <v>Animation completed</v>
       </c>
       <c r="E55" t="str">
         <v>Pass</v>
@@ -1418,16 +1418,16 @@
         <v>M-TC055</v>
       </c>
       <c r="B56" t="str">
-        <v>Generated mobile E2E test case M-TC055 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C56" t="str">
-        <v>Expected mobile app behavior for M-TC055</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D56" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E56" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="57">
@@ -1435,16 +1435,16 @@
         <v>M-TC056</v>
       </c>
       <c r="B57" t="str">
-        <v>Generated mobile E2E test case M-TC056 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C57" t="str">
-        <v>Expected mobile app behavior for M-TC056</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D57" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E57" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="58">
@@ -1452,16 +1452,16 @@
         <v>M-TC057</v>
       </c>
       <c r="B58" t="str">
-        <v>Generated mobile E2E test case M-TC057 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C58" t="str">
-        <v>Expected mobile app behavior for M-TC057</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D58" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E58" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="59">
@@ -1469,13 +1469,13 @@
         <v>M-TC058</v>
       </c>
       <c r="B59" t="str">
-        <v>Generated mobile E2E test case M-TC058 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C59" t="str">
-        <v>Expected mobile app behavior for M-TC058</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D59" t="str">
-        <v>Actual mobile app behavior for M-TC058</v>
+        <v>Animation completed</v>
       </c>
       <c r="E59" t="str">
         <v>Pass</v>
@@ -1486,16 +1486,16 @@
         <v>M-TC059</v>
       </c>
       <c r="B60" t="str">
-        <v>Generated mobile E2E test case M-TC059 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C60" t="str">
-        <v>Expected mobile app behavior for M-TC059</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D60" t="str">
-        <v>Actual mobile app behavior for M-TC059</v>
+        <v>Animation completed</v>
       </c>
       <c r="E60" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="61">
@@ -1503,16 +1503,16 @@
         <v>M-TC060</v>
       </c>
       <c r="B61" t="str">
-        <v>Generated mobile E2E test case M-TC060 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C61" t="str">
-        <v>Expected mobile app behavior for M-TC060</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D61" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E61" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="62">
@@ -1520,13 +1520,13 @@
         <v>M-TC061</v>
       </c>
       <c r="B62" t="str">
-        <v>Generated mobile E2E test case M-TC061 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C62" t="str">
-        <v>Expected mobile app behavior for M-TC061</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D62" t="str">
-        <v>Actual mobile app behavior for M-TC061</v>
+        <v>Animation completed</v>
       </c>
       <c r="E62" t="str">
         <v>Pass</v>
@@ -1537,13 +1537,13 @@
         <v>M-TC062</v>
       </c>
       <c r="B63" t="str">
-        <v>Generated mobile E2E test case M-TC062 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C63" t="str">
-        <v>Expected mobile app behavior for M-TC062</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D63" t="str">
-        <v>Actual mobile app behavior for M-TC062</v>
+        <v>Animation completed</v>
       </c>
       <c r="E63" t="str">
         <v>Pass</v>
@@ -1554,13 +1554,13 @@
         <v>M-TC063</v>
       </c>
       <c r="B64" t="str">
-        <v>Generated mobile E2E test case M-TC063 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C64" t="str">
-        <v>Expected mobile app behavior for M-TC063</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D64" t="str">
-        <v>Actual mobile app behavior for M-TC063</v>
+        <v>Animation completed</v>
       </c>
       <c r="E64" t="str">
         <v>Pass</v>
@@ -1571,16 +1571,16 @@
         <v>M-TC064</v>
       </c>
       <c r="B65" t="str">
-        <v>Generated mobile E2E test case M-TC064 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C65" t="str">
-        <v>Expected mobile app behavior for M-TC064</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D65" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E65" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="66">
@@ -1588,16 +1588,16 @@
         <v>M-TC065</v>
       </c>
       <c r="B66" t="str">
-        <v>Generated mobile E2E test case M-TC065 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C66" t="str">
-        <v>Expected mobile app behavior for M-TC065</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D66" t="str">
-        <v>Actual mobile app behavior for M-TC065</v>
+        <v>Animation completed</v>
       </c>
       <c r="E66" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="67">
@@ -1605,16 +1605,16 @@
         <v>M-TC066</v>
       </c>
       <c r="B67" t="str">
-        <v>Generated mobile E2E test case M-TC066 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C67" t="str">
-        <v>Expected mobile app behavior for M-TC066</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D67" t="str">
-        <v>Actual mobile app behavior for M-TC066</v>
+        <v>Animation completed</v>
       </c>
       <c r="E67" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="68">
@@ -1622,13 +1622,13 @@
         <v>M-TC067</v>
       </c>
       <c r="B68" t="str">
-        <v>Generated mobile E2E test case M-TC067 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C68" t="str">
-        <v>Expected mobile app behavior for M-TC067</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D68" t="str">
-        <v>Actual mobile app behavior for M-TC067</v>
+        <v>Animation completed</v>
       </c>
       <c r="E68" t="str">
         <v>Pass</v>
@@ -1639,16 +1639,16 @@
         <v>M-TC068</v>
       </c>
       <c r="B69" t="str">
-        <v>Generated mobile E2E test case M-TC068 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C69" t="str">
-        <v>Expected mobile app behavior for M-TC068</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D69" t="str">
-        <v>Actual mobile app behavior for M-TC068</v>
+        <v>Animation completed</v>
       </c>
       <c r="E69" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="70">
@@ -1656,16 +1656,16 @@
         <v>M-TC069</v>
       </c>
       <c r="B70" t="str">
-        <v>Generated mobile E2E test case M-TC069 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C70" t="str">
-        <v>Expected mobile app behavior for M-TC069</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D70" t="str">
-        <v>Actual mobile app behavior for M-TC069</v>
+        <v>Animation completed</v>
       </c>
       <c r="E70" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="71">
@@ -1673,16 +1673,16 @@
         <v>M-TC070</v>
       </c>
       <c r="B71" t="str">
-        <v>Generated mobile E2E test case M-TC070 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C71" t="str">
-        <v>Expected mobile app behavior for M-TC070</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D71" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E71" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="72">
@@ -1690,16 +1690,16 @@
         <v>M-TC071</v>
       </c>
       <c r="B72" t="str">
-        <v>Generated mobile E2E test case M-TC071 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C72" t="str">
-        <v>Expected mobile app behavior for M-TC071</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D72" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E72" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="73">
@@ -1707,16 +1707,16 @@
         <v>M-TC072</v>
       </c>
       <c r="B73" t="str">
-        <v>Generated mobile E2E test case M-TC072 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C73" t="str">
-        <v>Expected mobile app behavior for M-TC072</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D73" t="str">
-        <v>Actual mobile app behavior for M-TC072</v>
+        <v>Animation completed</v>
       </c>
       <c r="E73" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="74">
@@ -1724,13 +1724,13 @@
         <v>M-TC073</v>
       </c>
       <c r="B74" t="str">
-        <v>Generated mobile E2E test case M-TC073 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C74" t="str">
-        <v>Expected mobile app behavior for M-TC073</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D74" t="str">
-        <v>Actual mobile app behavior for M-TC073</v>
+        <v>Animation completed</v>
       </c>
       <c r="E74" t="str">
         <v>Pass</v>
@@ -1741,16 +1741,16 @@
         <v>M-TC074</v>
       </c>
       <c r="B75" t="str">
-        <v>Generated mobile E2E test case M-TC074 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C75" t="str">
-        <v>Expected mobile app behavior for M-TC074</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D75" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E75" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="76">
@@ -1758,13 +1758,13 @@
         <v>M-TC075</v>
       </c>
       <c r="B76" t="str">
-        <v>Generated mobile E2E test case M-TC075 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C76" t="str">
-        <v>Expected mobile app behavior for M-TC075</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D76" t="str">
-        <v>Actual mobile app behavior for M-TC075</v>
+        <v>Animation completed</v>
       </c>
       <c r="E76" t="str">
         <v>Pass</v>
@@ -1775,16 +1775,16 @@
         <v>M-TC076</v>
       </c>
       <c r="B77" t="str">
-        <v>Generated mobile E2E test case M-TC076 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C77" t="str">
-        <v>Expected mobile app behavior for M-TC076</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D77" t="str">
-        <v>Actual mobile app behavior for M-TC076</v>
+        <v>Animation completed</v>
       </c>
       <c r="E77" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="78">
@@ -1792,16 +1792,16 @@
         <v>M-TC077</v>
       </c>
       <c r="B78" t="str">
-        <v>Generated mobile E2E test case M-TC077 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C78" t="str">
-        <v>Expected mobile app behavior for M-TC077</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D78" t="str">
-        <v>Actual mobile app behavior for M-TC077</v>
+        <v>Animation completed</v>
       </c>
       <c r="E78" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="79">
@@ -1809,13 +1809,13 @@
         <v>M-TC078</v>
       </c>
       <c r="B79" t="str">
-        <v>Generated mobile E2E test case M-TC078 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C79" t="str">
-        <v>Expected mobile app behavior for M-TC078</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D79" t="str">
-        <v>Actual mobile app behavior for M-TC078</v>
+        <v>Animation completed</v>
       </c>
       <c r="E79" t="str">
         <v>Pass</v>
@@ -1826,13 +1826,13 @@
         <v>M-TC079</v>
       </c>
       <c r="B80" t="str">
-        <v>Generated mobile E2E test case M-TC079 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C80" t="str">
-        <v>Expected mobile app behavior for M-TC079</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D80" t="str">
-        <v>Actual mobile app behavior for M-TC079</v>
+        <v>Animation completed</v>
       </c>
       <c r="E80" t="str">
         <v>Pass</v>
@@ -1843,16 +1843,16 @@
         <v>M-TC080</v>
       </c>
       <c r="B81" t="str">
-        <v>Generated mobile E2E test case M-TC080 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C81" t="str">
-        <v>Expected mobile app behavior for M-TC080</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D81" t="str">
-        <v>Actual mobile app behavior for M-TC080</v>
+        <v>Animation completed</v>
       </c>
       <c r="E81" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="82">
@@ -1860,13 +1860,13 @@
         <v>M-TC081</v>
       </c>
       <c r="B82" t="str">
-        <v>Generated mobile E2E test case M-TC081 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C82" t="str">
-        <v>Expected mobile app behavior for M-TC081</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D82" t="str">
-        <v>Actual mobile app behavior for M-TC081</v>
+        <v>Animation completed</v>
       </c>
       <c r="E82" t="str">
         <v>Pass</v>
@@ -1877,13 +1877,13 @@
         <v>M-TC082</v>
       </c>
       <c r="B83" t="str">
-        <v>Generated mobile E2E test case M-TC082 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C83" t="str">
-        <v>Expected mobile app behavior for M-TC082</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D83" t="str">
-        <v>Actual mobile app behavior for M-TC082</v>
+        <v>Animation completed</v>
       </c>
       <c r="E83" t="str">
         <v>Pass</v>
@@ -1894,16 +1894,16 @@
         <v>M-TC083</v>
       </c>
       <c r="B84" t="str">
-        <v>Generated mobile E2E test case M-TC083 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C84" t="str">
-        <v>Expected mobile app behavior for M-TC083</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D84" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E84" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="85">
@@ -1911,13 +1911,13 @@
         <v>M-TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>Generated mobile E2E test case M-TC084 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C85" t="str">
-        <v>Expected mobile app behavior for M-TC084</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D85" t="str">
-        <v>Actual mobile app behavior for M-TC084</v>
+        <v>Animation completed</v>
       </c>
       <c r="E85" t="str">
         <v>Pass</v>
@@ -1928,13 +1928,13 @@
         <v>M-TC085</v>
       </c>
       <c r="B86" t="str">
-        <v>Generated mobile E2E test case M-TC085 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on App Bar triggers correct animation</v>
       </c>
       <c r="C86" t="str">
-        <v>Expected mobile app behavior for M-TC085</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D86" t="str">
-        <v>Actual mobile app behavior for M-TC085</v>
+        <v>Animation completed</v>
       </c>
       <c r="E86" t="str">
         <v>Pass</v>
@@ -1945,13 +1945,13 @@
         <v>M-TC086</v>
       </c>
       <c r="B87" t="str">
-        <v>Generated mobile E2E test case M-TC086 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C87" t="str">
-        <v>Expected mobile app behavior for M-TC086</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D87" t="str">
-        <v>Actual mobile app behavior for M-TC086</v>
+        <v>Animation completed</v>
       </c>
       <c r="E87" t="str">
         <v>Pass</v>
@@ -1962,16 +1962,16 @@
         <v>M-TC087</v>
       </c>
       <c r="B88" t="str">
-        <v>Generated mobile E2E test case M-TC087 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C88" t="str">
-        <v>Expected mobile app behavior for M-TC087</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D88" t="str">
-        <v>Actual mobile app behavior for M-TC087</v>
+        <v>Animation completed</v>
       </c>
       <c r="E88" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="89">
@@ -1979,13 +1979,13 @@
         <v>M-TC088</v>
       </c>
       <c r="B89" t="str">
-        <v>Generated mobile E2E test case M-TC088 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C89" t="str">
-        <v>Expected mobile app behavior for M-TC088</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D89" t="str">
-        <v>Actual mobile app behavior for M-TC088</v>
+        <v>Animation completed</v>
       </c>
       <c r="E89" t="str">
         <v>Pass</v>
@@ -1996,16 +1996,16 @@
         <v>M-TC089</v>
       </c>
       <c r="B90" t="str">
-        <v>Generated mobile E2E test case M-TC089 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on App Bar triggers correct animation</v>
       </c>
       <c r="C90" t="str">
-        <v>Expected mobile app behavior for M-TC089</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D90" t="str">
-        <v>Actual mobile app behavior for M-TC089</v>
+        <v>Animation completed</v>
       </c>
       <c r="E90" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="91">
@@ -2013,13 +2013,13 @@
         <v>M-TC090</v>
       </c>
       <c r="B91" t="str">
-        <v>Generated mobile E2E test case M-TC090 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C91" t="str">
-        <v>Expected mobile app behavior for M-TC090</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D91" t="str">
-        <v>Actual mobile app behavior for M-TC090</v>
+        <v>Animation completed</v>
       </c>
       <c r="E91" t="str">
         <v>Pass</v>
@@ -2030,13 +2030,13 @@
         <v>M-TC091</v>
       </c>
       <c r="B92" t="str">
-        <v>Generated mobile E2E test case M-TC091 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C92" t="str">
-        <v>Expected mobile app behavior for M-TC091</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D92" t="str">
-        <v>Actual mobile app behavior for M-TC091</v>
+        <v>Animation completed</v>
       </c>
       <c r="E92" t="str">
         <v>Pass</v>
@@ -2047,16 +2047,16 @@
         <v>M-TC092</v>
       </c>
       <c r="B93" t="str">
-        <v>Generated mobile E2E test case M-TC092 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C93" t="str">
-        <v>Expected mobile app behavior for M-TC092</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D93" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E93" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="94">
@@ -2064,16 +2064,16 @@
         <v>M-TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>Generated mobile E2E test case M-TC093 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C94" t="str">
-        <v>Expected mobile app behavior for M-TC093</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D94" t="str">
-        <v>Actual mobile app behavior for M-TC093</v>
+        <v>Animation completed</v>
       </c>
       <c r="E94" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="95">
@@ -2081,13 +2081,13 @@
         <v>M-TC094</v>
       </c>
       <c r="B95" t="str">
-        <v>Generated mobile E2E test case M-TC094 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C95" t="str">
-        <v>Expected mobile app behavior for M-TC094</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D95" t="str">
-        <v>Actual mobile app behavior for M-TC094</v>
+        <v>Animation completed</v>
       </c>
       <c r="E95" t="str">
         <v>Pass</v>
@@ -2098,13 +2098,13 @@
         <v>M-TC095</v>
       </c>
       <c r="B96" t="str">
-        <v>Generated mobile E2E test case M-TC095 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on App Bar triggers correct animation</v>
       </c>
       <c r="C96" t="str">
-        <v>Expected mobile app behavior for M-TC095</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D96" t="str">
-        <v>Actual mobile app behavior for M-TC095</v>
+        <v>Animation completed</v>
       </c>
       <c r="E96" t="str">
         <v>Pass</v>
@@ -2115,13 +2115,13 @@
         <v>M-TC096</v>
       </c>
       <c r="B97" t="str">
-        <v>Generated mobile E2E test case M-TC096 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C97" t="str">
-        <v>Expected mobile app behavior for M-TC096</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D97" t="str">
-        <v>Actual mobile app behavior for M-TC096</v>
+        <v>Animation completed</v>
       </c>
       <c r="E97" t="str">
         <v>Pass</v>
@@ -2132,13 +2132,13 @@
         <v>M-TC097</v>
       </c>
       <c r="B98" t="str">
-        <v>Generated mobile E2E test case M-TC097 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C98" t="str">
-        <v>Expected mobile app behavior for M-TC097</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D98" t="str">
-        <v>Actual mobile app behavior for M-TC097</v>
+        <v>Animation completed</v>
       </c>
       <c r="E98" t="str">
         <v>Pass</v>
@@ -2149,13 +2149,13 @@
         <v>M-TC098</v>
       </c>
       <c r="B99" t="str">
-        <v>Generated mobile E2E test case M-TC098 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C99" t="str">
-        <v>Expected mobile app behavior for M-TC098</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D99" t="str">
-        <v>Actual mobile app behavior for M-TC098</v>
+        <v>Animation completed</v>
       </c>
       <c r="E99" t="str">
         <v>Pass</v>
@@ -2166,16 +2166,16 @@
         <v>M-TC099</v>
       </c>
       <c r="B100" t="str">
-        <v>Generated mobile E2E test case M-TC099 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on App Bar triggers correct animation</v>
       </c>
       <c r="C100" t="str">
-        <v>Expected mobile app behavior for M-TC099</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D100" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E100" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="101">
@@ -2183,13 +2183,13 @@
         <v>M-TC100</v>
       </c>
       <c r="B101" t="str">
-        <v>Generated mobile E2E test case M-TC100 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C101" t="str">
-        <v>Expected mobile app behavior for M-TC100</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D101" t="str">
-        <v>Actual mobile app behavior for M-TC100</v>
+        <v>Animation completed</v>
       </c>
       <c r="E101" t="str">
         <v>Pass</v>
@@ -2200,16 +2200,16 @@
         <v>M-TC101</v>
       </c>
       <c r="B102" t="str">
-        <v>Generated mobile E2E test case M-TC101 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C102" t="str">
-        <v>Expected mobile app behavior for M-TC101</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D102" t="str">
-        <v>Actual mobile app behavior for M-TC101</v>
+        <v>Animation completed</v>
       </c>
       <c r="E102" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="103">
@@ -2217,16 +2217,16 @@
         <v>M-TC102</v>
       </c>
       <c r="B103" t="str">
-        <v>Generated mobile E2E test case M-TC102 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C103" t="str">
-        <v>Expected mobile app behavior for M-TC102</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D103" t="str">
-        <v>Actual mobile app behavior for M-TC102</v>
+        <v>Animation completed</v>
       </c>
       <c r="E103" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="104">
@@ -2234,13 +2234,13 @@
         <v>M-TC103</v>
       </c>
       <c r="B104" t="str">
-        <v>Generated mobile E2E test case M-TC103 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C104" t="str">
-        <v>Expected mobile app behavior for M-TC103</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D104" t="str">
-        <v>Actual mobile app behavior for M-TC103</v>
+        <v>Animation completed</v>
       </c>
       <c r="E104" t="str">
         <v>Pass</v>
@@ -2251,13 +2251,13 @@
         <v>M-TC104</v>
       </c>
       <c r="B105" t="str">
-        <v>Generated mobile E2E test case M-TC104 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C105" t="str">
-        <v>Expected mobile app behavior for M-TC104</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D105" t="str">
-        <v>Actual mobile app behavior for M-TC104</v>
+        <v>Animation completed</v>
       </c>
       <c r="E105" t="str">
         <v>Pass</v>
@@ -2268,13 +2268,13 @@
         <v>M-TC105</v>
       </c>
       <c r="B106" t="str">
-        <v>Generated mobile E2E test case M-TC105 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C106" t="str">
-        <v>Expected mobile app behavior for M-TC105</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D106" t="str">
-        <v>Actual mobile app behavior for M-TC105</v>
+        <v>Animation completed</v>
       </c>
       <c r="E106" t="str">
         <v>Pass</v>
@@ -2285,13 +2285,13 @@
         <v>M-TC106</v>
       </c>
       <c r="B107" t="str">
-        <v>Generated mobile E2E test case M-TC106 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C107" t="str">
-        <v>Expected mobile app behavior for M-TC106</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D107" t="str">
-        <v>Actual mobile app behavior for M-TC106</v>
+        <v>Animation completed</v>
       </c>
       <c r="E107" t="str">
         <v>Pass</v>
@@ -2302,13 +2302,13 @@
         <v>M-TC107</v>
       </c>
       <c r="B108" t="str">
-        <v>Generated mobile E2E test case M-TC107 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on App Bar triggers correct animation</v>
       </c>
       <c r="C108" t="str">
-        <v>Expected mobile app behavior for M-TC107</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D108" t="str">
-        <v>Actual mobile app behavior for M-TC107</v>
+        <v>Animation completed</v>
       </c>
       <c r="E108" t="str">
         <v>Pass</v>
@@ -2319,16 +2319,16 @@
         <v>M-TC108</v>
       </c>
       <c r="B109" t="str">
-        <v>Generated mobile E2E test case M-TC108 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C109" t="str">
-        <v>Expected mobile app behavior for M-TC108</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D109" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E109" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="110">
@@ -2336,13 +2336,13 @@
         <v>M-TC109</v>
       </c>
       <c r="B110" t="str">
-        <v>Generated mobile E2E test case M-TC109 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C110" t="str">
-        <v>Expected mobile app behavior for M-TC109</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D110" t="str">
-        <v>Actual mobile app behavior for M-TC109</v>
+        <v>Animation completed</v>
       </c>
       <c r="E110" t="str">
         <v>Pass</v>
@@ -2353,13 +2353,13 @@
         <v>M-TC110</v>
       </c>
       <c r="B111" t="str">
-        <v>Generated mobile E2E test case M-TC110 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on App Bar triggers correct animation</v>
       </c>
       <c r="C111" t="str">
-        <v>Expected mobile app behavior for M-TC110</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D111" t="str">
-        <v>Actual mobile app behavior for M-TC110</v>
+        <v>Animation completed</v>
       </c>
       <c r="E111" t="str">
         <v>Pass</v>
@@ -2370,13 +2370,13 @@
         <v>M-TC111</v>
       </c>
       <c r="B112" t="str">
-        <v>Generated mobile E2E test case M-TC111 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C112" t="str">
-        <v>Expected mobile app behavior for M-TC111</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D112" t="str">
-        <v>Actual mobile app behavior for M-TC111</v>
+        <v>Animation completed</v>
       </c>
       <c r="E112" t="str">
         <v>Pass</v>
@@ -2387,13 +2387,13 @@
         <v>M-TC112</v>
       </c>
       <c r="B113" t="str">
-        <v>Generated mobile E2E test case M-TC112 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C113" t="str">
-        <v>Expected mobile app behavior for M-TC112</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D113" t="str">
-        <v>Actual mobile app behavior for M-TC112</v>
+        <v>Animation completed</v>
       </c>
       <c r="E113" t="str">
         <v>Pass</v>
@@ -2404,13 +2404,13 @@
         <v>M-TC113</v>
       </c>
       <c r="B114" t="str">
-        <v>Generated mobile E2E test case M-TC113 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C114" t="str">
-        <v>Expected mobile app behavior for M-TC113</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D114" t="str">
-        <v>Actual mobile app behavior for M-TC113</v>
+        <v>Animation completed</v>
       </c>
       <c r="E114" t="str">
         <v>Pass</v>
@@ -2421,13 +2421,13 @@
         <v>M-TC114</v>
       </c>
       <c r="B115" t="str">
-        <v>Generated mobile E2E test case M-TC114 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C115" t="str">
-        <v>Expected mobile app behavior for M-TC114</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D115" t="str">
-        <v>Actual mobile app behavior for M-TC114</v>
+        <v>Animation completed</v>
       </c>
       <c r="E115" t="str">
         <v>Pass</v>
@@ -2438,16 +2438,16 @@
         <v>M-TC115</v>
       </c>
       <c r="B116" t="str">
-        <v>Generated mobile E2E test case M-TC115 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C116" t="str">
-        <v>Expected mobile app behavior for M-TC115</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D116" t="str">
-        <v>Actual mobile app behavior for M-TC115</v>
+        <v>Animation completed</v>
       </c>
       <c r="E116" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="117">
@@ -2455,13 +2455,13 @@
         <v>M-TC116</v>
       </c>
       <c r="B117" t="str">
-        <v>Generated mobile E2E test case M-TC116 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C117" t="str">
-        <v>Expected mobile app behavior for M-TC116</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D117" t="str">
-        <v>Actual mobile app behavior for M-TC116</v>
+        <v>Animation completed</v>
       </c>
       <c r="E117" t="str">
         <v>Pass</v>
@@ -2472,13 +2472,13 @@
         <v>M-TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>Generated mobile E2E test case M-TC117 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C118" t="str">
-        <v>Expected mobile app behavior for M-TC117</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D118" t="str">
-        <v>Actual mobile app behavior for M-TC117</v>
+        <v>Animation completed</v>
       </c>
       <c r="E118" t="str">
         <v>Pass</v>
@@ -2489,16 +2489,16 @@
         <v>M-TC118</v>
       </c>
       <c r="B119" t="str">
-        <v>Generated mobile E2E test case M-TC118 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C119" t="str">
-        <v>Expected mobile app behavior for M-TC118</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D119" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E119" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="120">
@@ -2506,13 +2506,13 @@
         <v>M-TC119</v>
       </c>
       <c r="B120" t="str">
-        <v>Generated mobile E2E test case M-TC119 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C120" t="str">
-        <v>Expected mobile app behavior for M-TC119</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D120" t="str">
-        <v>Actual mobile app behavior for M-TC119</v>
+        <v>Animation completed</v>
       </c>
       <c r="E120" t="str">
         <v>Pass</v>
@@ -2523,13 +2523,13 @@
         <v>M-TC120</v>
       </c>
       <c r="B121" t="str">
-        <v>Generated mobile E2E test case M-TC120 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C121" t="str">
-        <v>Expected mobile app behavior for M-TC120</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D121" t="str">
-        <v>Actual mobile app behavior for M-TC120</v>
+        <v>Animation completed</v>
       </c>
       <c r="E121" t="str">
         <v>Pass</v>
@@ -2540,16 +2540,16 @@
         <v>M-TC121</v>
       </c>
       <c r="B122" t="str">
-        <v>Generated mobile E2E test case M-TC121 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C122" t="str">
-        <v>Expected mobile app behavior for M-TC121</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D122" t="str">
-        <v>Actual mobile app behavior for M-TC121</v>
+        <v>Animation completed</v>
       </c>
       <c r="E122" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="123">
@@ -2557,16 +2557,16 @@
         <v>M-TC122</v>
       </c>
       <c r="B123" t="str">
-        <v>Generated mobile E2E test case M-TC122 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C123" t="str">
-        <v>Expected mobile app behavior for M-TC122</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D123" t="str">
-        <v>Actual mobile app behavior for M-TC122</v>
+        <v>Animation completed</v>
       </c>
       <c r="E123" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="124">
@@ -2574,13 +2574,13 @@
         <v>M-TC123</v>
       </c>
       <c r="B124" t="str">
-        <v>Generated mobile E2E test case M-TC123 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on App Bar triggers correct animation</v>
       </c>
       <c r="C124" t="str">
-        <v>Expected mobile app behavior for M-TC123</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D124" t="str">
-        <v>Actual mobile app behavior for M-TC123</v>
+        <v>Animation completed</v>
       </c>
       <c r="E124" t="str">
         <v>Pass</v>
@@ -2591,13 +2591,13 @@
         <v>M-TC124</v>
       </c>
       <c r="B125" t="str">
-        <v>Generated mobile E2E test case M-TC124 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C125" t="str">
-        <v>Expected mobile app behavior for M-TC124</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D125" t="str">
-        <v>Actual mobile app behavior for M-TC124</v>
+        <v>Animation completed</v>
       </c>
       <c r="E125" t="str">
         <v>Pass</v>
@@ -2608,13 +2608,13 @@
         <v>M-TC125</v>
       </c>
       <c r="B126" t="str">
-        <v>Generated mobile E2E test case M-TC125 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C126" t="str">
-        <v>Expected mobile app behavior for M-TC125</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D126" t="str">
-        <v>Actual mobile app behavior for M-TC125</v>
+        <v>Animation completed</v>
       </c>
       <c r="E126" t="str">
         <v>Pass</v>
@@ -2625,16 +2625,16 @@
         <v>M-TC126</v>
       </c>
       <c r="B127" t="str">
-        <v>Generated mobile E2E test case M-TC126 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C127" t="str">
-        <v>Expected mobile app behavior for M-TC126</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D127" t="str">
-        <v>Actual mobile app behavior for M-TC126</v>
+        <v>Animation completed</v>
       </c>
       <c r="E127" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="128">
@@ -2642,13 +2642,13 @@
         <v>M-TC127</v>
       </c>
       <c r="B128" t="str">
-        <v>Generated mobile E2E test case M-TC127 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C128" t="str">
-        <v>Expected mobile app behavior for M-TC127</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D128" t="str">
-        <v>Actual mobile app behavior for M-TC127</v>
+        <v>Animation completed</v>
       </c>
       <c r="E128" t="str">
         <v>Pass</v>
@@ -2659,13 +2659,13 @@
         <v>M-TC128</v>
       </c>
       <c r="B129" t="str">
-        <v>Generated mobile E2E test case M-TC128 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C129" t="str">
-        <v>Expected mobile app behavior for M-TC128</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D129" t="str">
-        <v>Actual mobile app behavior for M-TC128</v>
+        <v>Animation completed</v>
       </c>
       <c r="E129" t="str">
         <v>Pass</v>
@@ -2676,16 +2676,16 @@
         <v>M-TC129</v>
       </c>
       <c r="B130" t="str">
-        <v>Generated mobile E2E test case M-TC129 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C130" t="str">
-        <v>Expected mobile app behavior for M-TC129</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D130" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E130" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="131">
@@ -2693,16 +2693,16 @@
         <v>M-TC130</v>
       </c>
       <c r="B131" t="str">
-        <v>Generated mobile E2E test case M-TC130 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C131" t="str">
-        <v>Expected mobile app behavior for M-TC130</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D131" t="str">
-        <v>Actual mobile app behavior for M-TC130</v>
+        <v>Animation completed</v>
       </c>
       <c r="E131" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="132">
@@ -2710,16 +2710,16 @@
         <v>M-TC131</v>
       </c>
       <c r="B132" t="str">
-        <v>Generated mobile E2E test case M-TC131 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C132" t="str">
-        <v>Expected mobile app behavior for M-TC131</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D132" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E132" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="133">
@@ -2727,13 +2727,13 @@
         <v>M-TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>Generated mobile E2E test case M-TC132 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C133" t="str">
-        <v>Expected mobile app behavior for M-TC132</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D133" t="str">
-        <v>Actual mobile app behavior for M-TC132</v>
+        <v>Animation completed</v>
       </c>
       <c r="E133" t="str">
         <v>Pass</v>
@@ -2744,13 +2744,13 @@
         <v>M-TC133</v>
       </c>
       <c r="B134" t="str">
-        <v>Generated mobile E2E test case M-TC133 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on App Bar triggers correct animation</v>
       </c>
       <c r="C134" t="str">
-        <v>Expected mobile app behavior for M-TC133</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D134" t="str">
-        <v>Actual mobile app behavior for M-TC133</v>
+        <v>Animation completed</v>
       </c>
       <c r="E134" t="str">
         <v>Pass</v>
@@ -2761,13 +2761,13 @@
         <v>M-TC134</v>
       </c>
       <c r="B135" t="str">
-        <v>Generated mobile E2E test case M-TC134 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C135" t="str">
-        <v>Expected mobile app behavior for M-TC134</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D135" t="str">
-        <v>Actual mobile app behavior for M-TC134</v>
+        <v>Animation completed</v>
       </c>
       <c r="E135" t="str">
         <v>Pass</v>
@@ -2778,13 +2778,13 @@
         <v>M-TC135</v>
       </c>
       <c r="B136" t="str">
-        <v>Generated mobile E2E test case M-TC135 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C136" t="str">
-        <v>Expected mobile app behavior for M-TC135</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D136" t="str">
-        <v>Actual mobile app behavior for M-TC135</v>
+        <v>Animation completed</v>
       </c>
       <c r="E136" t="str">
         <v>Pass</v>
@@ -2795,13 +2795,13 @@
         <v>M-TC136</v>
       </c>
       <c r="B137" t="str">
-        <v>Generated mobile E2E test case M-TC136 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C137" t="str">
-        <v>Expected mobile app behavior for M-TC136</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D137" t="str">
-        <v>Actual mobile app behavior for M-TC136</v>
+        <v>Animation completed</v>
       </c>
       <c r="E137" t="str">
         <v>Pass</v>
@@ -2812,16 +2812,16 @@
         <v>M-TC137</v>
       </c>
       <c r="B138" t="str">
-        <v>Generated mobile E2E test case M-TC137 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C138" t="str">
-        <v>Expected mobile app behavior for M-TC137</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D138" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E138" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="139">
@@ -2829,13 +2829,13 @@
         <v>M-TC138</v>
       </c>
       <c r="B139" t="str">
-        <v>Generated mobile E2E test case M-TC138 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C139" t="str">
-        <v>Expected mobile app behavior for M-TC138</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D139" t="str">
-        <v>Actual mobile app behavior for M-TC138</v>
+        <v>Animation completed</v>
       </c>
       <c r="E139" t="str">
         <v>Pass</v>
@@ -2846,16 +2846,16 @@
         <v>M-TC139</v>
       </c>
       <c r="B140" t="str">
-        <v>Generated mobile E2E test case M-TC139 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C140" t="str">
-        <v>Expected mobile app behavior for M-TC139</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D140" t="str">
-        <v>Actual mobile app behavior for M-TC139</v>
+        <v>Animation completed</v>
       </c>
       <c r="E140" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="141">
@@ -2863,13 +2863,13 @@
         <v>M-TC140</v>
       </c>
       <c r="B141" t="str">
-        <v>Generated mobile E2E test case M-TC140 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C141" t="str">
-        <v>Expected mobile app behavior for M-TC140</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D141" t="str">
-        <v>Actual mobile app behavior for M-TC140</v>
+        <v>Animation completed</v>
       </c>
       <c r="E141" t="str">
         <v>Pass</v>
@@ -2880,13 +2880,13 @@
         <v>M-TC141</v>
       </c>
       <c r="B142" t="str">
-        <v>Generated mobile E2E test case M-TC141 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C142" t="str">
-        <v>Expected mobile app behavior for M-TC141</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D142" t="str">
-        <v>Actual mobile app behavior for M-TC141</v>
+        <v>Animation completed</v>
       </c>
       <c r="E142" t="str">
         <v>Pass</v>
@@ -2897,13 +2897,13 @@
         <v>M-TC142</v>
       </c>
       <c r="B143" t="str">
-        <v>Generated mobile E2E test case M-TC142 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C143" t="str">
-        <v>Expected mobile app behavior for M-TC142</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D143" t="str">
-        <v>Actual mobile app behavior for M-TC142</v>
+        <v>Animation completed</v>
       </c>
       <c r="E143" t="str">
         <v>Pass</v>
@@ -2914,16 +2914,16 @@
         <v>M-TC143</v>
       </c>
       <c r="B144" t="str">
-        <v>Generated mobile E2E test case M-TC143 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C144" t="str">
-        <v>Expected mobile app behavior for M-TC143</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D144" t="str">
-        <v>Actual mobile app behavior for M-TC143</v>
+        <v>Animation completed</v>
       </c>
       <c r="E144" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="145">
@@ -2931,16 +2931,16 @@
         <v>M-TC144</v>
       </c>
       <c r="B145" t="str">
-        <v>Generated mobile E2E test case M-TC144 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C145" t="str">
-        <v>Expected mobile app behavior for M-TC144</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D145" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E145" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="146">
@@ -2948,13 +2948,13 @@
         <v>M-TC145</v>
       </c>
       <c r="B146" t="str">
-        <v>Generated mobile E2E test case M-TC145 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C146" t="str">
-        <v>Expected mobile app behavior for M-TC145</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D146" t="str">
-        <v>Actual mobile app behavior for M-TC145</v>
+        <v>Animation completed</v>
       </c>
       <c r="E146" t="str">
         <v>Pass</v>
@@ -2965,13 +2965,13 @@
         <v>M-TC146</v>
       </c>
       <c r="B147" t="str">
-        <v>Generated mobile E2E test case M-TC146 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C147" t="str">
-        <v>Expected mobile app behavior for M-TC146</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D147" t="str">
-        <v>Actual mobile app behavior for M-TC146</v>
+        <v>Animation completed</v>
       </c>
       <c r="E147" t="str">
         <v>Pass</v>
@@ -2982,13 +2982,13 @@
         <v>M-TC147</v>
       </c>
       <c r="B148" t="str">
-        <v>Generated mobile E2E test case M-TC147 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C148" t="str">
-        <v>Expected mobile app behavior for M-TC147</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D148" t="str">
-        <v>Actual mobile app behavior for M-TC147</v>
+        <v>Animation completed</v>
       </c>
       <c r="E148" t="str">
         <v>Pass</v>
@@ -2999,16 +2999,16 @@
         <v>M-TC148</v>
       </c>
       <c r="B149" t="str">
-        <v>Generated mobile E2E test case M-TC148 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C149" t="str">
-        <v>Expected mobile app behavior for M-TC148</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D149" t="str">
-        <v>Actual mobile app behavior for M-TC148</v>
+        <v>Animation completed</v>
       </c>
       <c r="E149" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="150">
@@ -3016,13 +3016,13 @@
         <v>M-TC149</v>
       </c>
       <c r="B150" t="str">
-        <v>Generated mobile E2E test case M-TC149 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C150" t="str">
-        <v>Expected mobile app behavior for M-TC149</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D150" t="str">
-        <v>Actual mobile app behavior for M-TC149</v>
+        <v>Animation completed</v>
       </c>
       <c r="E150" t="str">
         <v>Pass</v>
@@ -3033,16 +3033,16 @@
         <v>M-TC150</v>
       </c>
       <c r="B151" t="str">
-        <v>Generated mobile E2E test case M-TC150 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C151" t="str">
-        <v>Expected mobile app behavior for M-TC150</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D151" t="str">
-        <v>Actual mobile app behavior for M-TC150</v>
+        <v>Animation completed</v>
       </c>
       <c r="E151" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="152">
@@ -3050,16 +3050,16 @@
         <v>M-TC151</v>
       </c>
       <c r="B152" t="str">
-        <v>Generated mobile E2E test case M-TC151 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C152" t="str">
-        <v>Expected mobile app behavior for M-TC151</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D152" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E152" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="153">
@@ -3067,16 +3067,16 @@
         <v>M-TC152</v>
       </c>
       <c r="B153" t="str">
-        <v>Generated mobile E2E test case M-TC152 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C153" t="str">
-        <v>Expected mobile app behavior for M-TC152</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D153" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E153" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="154">
@@ -3084,13 +3084,13 @@
         <v>M-TC153</v>
       </c>
       <c r="B154" t="str">
-        <v>Generated mobile E2E test case M-TC153 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C154" t="str">
-        <v>Expected mobile app behavior for M-TC153</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D154" t="str">
-        <v>Actual mobile app behavior for M-TC153</v>
+        <v>Animation completed</v>
       </c>
       <c r="E154" t="str">
         <v>Pass</v>
@@ -3101,13 +3101,13 @@
         <v>M-TC154</v>
       </c>
       <c r="B155" t="str">
-        <v>Generated mobile E2E test case M-TC154 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C155" t="str">
-        <v>Expected mobile app behavior for M-TC154</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D155" t="str">
-        <v>Actual mobile app behavior for M-TC154</v>
+        <v>Animation completed</v>
       </c>
       <c r="E155" t="str">
         <v>Pass</v>
@@ -3118,13 +3118,13 @@
         <v>M-TC155</v>
       </c>
       <c r="B156" t="str">
-        <v>Generated mobile E2E test case M-TC155 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C156" t="str">
-        <v>Expected mobile app behavior for M-TC155</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D156" t="str">
-        <v>Actual mobile app behavior for M-TC155</v>
+        <v>Animation completed</v>
       </c>
       <c r="E156" t="str">
         <v>Pass</v>
@@ -3135,13 +3135,13 @@
         <v>M-TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>Generated mobile E2E test case M-TC156 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C157" t="str">
-        <v>Expected mobile app behavior for M-TC156</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D157" t="str">
-        <v>Actual mobile app behavior for M-TC156</v>
+        <v>Animation completed</v>
       </c>
       <c r="E157" t="str">
         <v>Pass</v>
@@ -3152,16 +3152,16 @@
         <v>M-TC157</v>
       </c>
       <c r="B158" t="str">
-        <v>Generated mobile E2E test case M-TC157 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C158" t="str">
-        <v>Expected mobile app behavior for M-TC157</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D158" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E158" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="159">
@@ -3169,13 +3169,13 @@
         <v>M-TC158</v>
       </c>
       <c r="B159" t="str">
-        <v>Generated mobile E2E test case M-TC158 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C159" t="str">
-        <v>Expected mobile app behavior for M-TC158</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D159" t="str">
-        <v>Actual mobile app behavior for M-TC158</v>
+        <v>Animation completed</v>
       </c>
       <c r="E159" t="str">
         <v>Pass</v>
@@ -3186,16 +3186,16 @@
         <v>M-TC159</v>
       </c>
       <c r="B160" t="str">
-        <v>Generated mobile E2E test case M-TC159 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C160" t="str">
-        <v>Expected mobile app behavior for M-TC159</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D160" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E160" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="161">
@@ -3203,16 +3203,16 @@
         <v>M-TC160</v>
       </c>
       <c r="B161" t="str">
-        <v>Generated mobile E2E test case M-TC160 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C161" t="str">
-        <v>Expected mobile app behavior for M-TC160</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D161" t="str">
-        <v>Actual mobile app behavior for M-TC160</v>
+        <v>Animation completed</v>
       </c>
       <c r="E161" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="162">
@@ -3220,16 +3220,16 @@
         <v>M-TC161</v>
       </c>
       <c r="B162" t="str">
-        <v>Generated mobile E2E test case M-TC161 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C162" t="str">
-        <v>Expected mobile app behavior for M-TC161</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D162" t="str">
-        <v>Actual mobile app behavior for M-TC161</v>
+        <v>Animation completed</v>
       </c>
       <c r="E162" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="163">
@@ -3237,13 +3237,13 @@
         <v>M-TC162</v>
       </c>
       <c r="B163" t="str">
-        <v>Generated mobile E2E test case M-TC162 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C163" t="str">
-        <v>Expected mobile app behavior for M-TC162</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D163" t="str">
-        <v>Actual mobile app behavior for M-TC162</v>
+        <v>Animation completed</v>
       </c>
       <c r="E163" t="str">
         <v>Pass</v>
@@ -3254,13 +3254,13 @@
         <v>M-TC163</v>
       </c>
       <c r="B164" t="str">
-        <v>Generated mobile E2E test case M-TC163 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C164" t="str">
-        <v>Expected mobile app behavior for M-TC163</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D164" t="str">
-        <v>Actual mobile app behavior for M-TC163</v>
+        <v>Animation completed</v>
       </c>
       <c r="E164" t="str">
         <v>Pass</v>
@@ -3271,13 +3271,13 @@
         <v>M-TC164</v>
       </c>
       <c r="B165" t="str">
-        <v>Generated mobile E2E test case M-TC164 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C165" t="str">
-        <v>Expected mobile app behavior for M-TC164</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D165" t="str">
-        <v>Actual mobile app behavior for M-TC164</v>
+        <v>Animation completed</v>
       </c>
       <c r="E165" t="str">
         <v>Pass</v>
@@ -3288,13 +3288,13 @@
         <v>M-TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>Generated mobile E2E test case M-TC165 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C166" t="str">
-        <v>Expected mobile app behavior for M-TC165</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D166" t="str">
-        <v>Actual mobile app behavior for M-TC165</v>
+        <v>Animation completed</v>
       </c>
       <c r="E166" t="str">
         <v>Pass</v>
@@ -3305,16 +3305,16 @@
         <v>M-TC166</v>
       </c>
       <c r="B167" t="str">
-        <v>Generated mobile E2E test case M-TC166 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C167" t="str">
-        <v>Expected mobile app behavior for M-TC166</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D167" t="str">
-        <v>Actual mobile app behavior for M-TC166</v>
+        <v>Animation completed</v>
       </c>
       <c r="E167" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="168">
@@ -3322,16 +3322,16 @@
         <v>M-TC167</v>
       </c>
       <c r="B168" t="str">
-        <v>Generated mobile E2E test case M-TC167 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C168" t="str">
-        <v>Expected mobile app behavior for M-TC167</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D168" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E168" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="169">
@@ -3339,13 +3339,13 @@
         <v>M-TC168</v>
       </c>
       <c r="B169" t="str">
-        <v>Generated mobile E2E test case M-TC168 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C169" t="str">
-        <v>Expected mobile app behavior for M-TC168</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D169" t="str">
-        <v>Actual mobile app behavior for M-TC168</v>
+        <v>Animation completed</v>
       </c>
       <c r="E169" t="str">
         <v>Pass</v>
@@ -3356,13 +3356,13 @@
         <v>M-TC169</v>
       </c>
       <c r="B170" t="str">
-        <v>Generated mobile E2E test case M-TC169 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on App Bar triggers correct animation</v>
       </c>
       <c r="C170" t="str">
-        <v>Expected mobile app behavior for M-TC169</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D170" t="str">
-        <v>Actual mobile app behavior for M-TC169</v>
+        <v>Animation completed</v>
       </c>
       <c r="E170" t="str">
         <v>Pass</v>
@@ -3373,16 +3373,16 @@
         <v>M-TC170</v>
       </c>
       <c r="B171" t="str">
-        <v>Generated mobile E2E test case M-TC170 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C171" t="str">
-        <v>Expected mobile app behavior for M-TC170</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D171" t="str">
-        <v>Actual mobile app behavior for M-TC170</v>
+        <v>Animation completed</v>
       </c>
       <c r="E171" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="172">
@@ -3390,13 +3390,13 @@
         <v>M-TC171</v>
       </c>
       <c r="B172" t="str">
-        <v>Generated mobile E2E test case M-TC171 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C172" t="str">
-        <v>Expected mobile app behavior for M-TC171</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D172" t="str">
-        <v>Actual mobile app behavior for M-TC171</v>
+        <v>Animation completed</v>
       </c>
       <c r="E172" t="str">
         <v>Pass</v>
@@ -3407,16 +3407,16 @@
         <v>M-TC172</v>
       </c>
       <c r="B173" t="str">
-        <v>Generated mobile E2E test case M-TC172 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C173" t="str">
-        <v>Expected mobile app behavior for M-TC172</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D173" t="str">
-        <v>Actual mobile app behavior for M-TC172</v>
+        <v>Animation completed</v>
       </c>
       <c r="E173" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="174">
@@ -3424,13 +3424,13 @@
         <v>M-TC173</v>
       </c>
       <c r="B174" t="str">
-        <v>Generated mobile E2E test case M-TC173 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C174" t="str">
-        <v>Expected mobile app behavior for M-TC173</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D174" t="str">
-        <v>Actual mobile app behavior for M-TC173</v>
+        <v>Animation completed</v>
       </c>
       <c r="E174" t="str">
         <v>Pass</v>
@@ -3441,16 +3441,16 @@
         <v>M-TC174</v>
       </c>
       <c r="B175" t="str">
-        <v>Generated mobile E2E test case M-TC174 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C175" t="str">
-        <v>Expected mobile app behavior for M-TC174</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D175" t="str">
-        <v>Actual mobile app behavior for M-TC174</v>
+        <v>Animation completed</v>
       </c>
       <c r="E175" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="176">
@@ -3458,16 +3458,16 @@
         <v>M-TC175</v>
       </c>
       <c r="B176" t="str">
-        <v>Generated mobile E2E test case M-TC175 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C176" t="str">
-        <v>Expected mobile app behavior for M-TC175</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D176" t="str">
-        <v>Actual mobile app behavior for M-TC175</v>
+        <v>Animation completed</v>
       </c>
       <c r="E176" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="177">
@@ -3475,16 +3475,16 @@
         <v>M-TC176</v>
       </c>
       <c r="B177" t="str">
-        <v>Generated mobile E2E test case M-TC176 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C177" t="str">
-        <v>Expected mobile app behavior for M-TC176</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D177" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E177" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="178">
@@ -3492,16 +3492,16 @@
         <v>M-TC177</v>
       </c>
       <c r="B178" t="str">
-        <v>Generated mobile E2E test case M-TC177 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C178" t="str">
-        <v>Expected mobile app behavior for M-TC177</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D178" t="str">
-        <v>Actual mobile app behavior for M-TC177</v>
+        <v>Animation completed</v>
       </c>
       <c r="E178" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="179">
@@ -3509,13 +3509,13 @@
         <v>M-TC178</v>
       </c>
       <c r="B179" t="str">
-        <v>Generated mobile E2E test case M-TC178 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C179" t="str">
-        <v>Expected mobile app behavior for M-TC178</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D179" t="str">
-        <v>Actual mobile app behavior for M-TC178</v>
+        <v>Animation completed</v>
       </c>
       <c r="E179" t="str">
         <v>Pass</v>
@@ -3526,13 +3526,13 @@
         <v>M-TC179</v>
       </c>
       <c r="B180" t="str">
-        <v>Generated mobile E2E test case M-TC179 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C180" t="str">
-        <v>Expected mobile app behavior for M-TC179</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D180" t="str">
-        <v>Actual mobile app behavior for M-TC179</v>
+        <v>Animation completed</v>
       </c>
       <c r="E180" t="str">
         <v>Pass</v>
@@ -3543,16 +3543,16 @@
         <v>M-TC180</v>
       </c>
       <c r="B181" t="str">
-        <v>Generated mobile E2E test case M-TC180 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C181" t="str">
-        <v>Expected mobile app behavior for M-TC180</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D181" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E181" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="182">
@@ -3560,16 +3560,16 @@
         <v>M-TC181</v>
       </c>
       <c r="B182" t="str">
-        <v>Generated mobile E2E test case M-TC181 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C182" t="str">
-        <v>Expected mobile app behavior for M-TC181</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D182" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E182" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="183">
@@ -3577,16 +3577,16 @@
         <v>M-TC182</v>
       </c>
       <c r="B183" t="str">
-        <v>Generated mobile E2E test case M-TC182 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C183" t="str">
-        <v>Expected mobile app behavior for M-TC182</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D183" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E183" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="184">
@@ -3594,16 +3594,16 @@
         <v>M-TC183</v>
       </c>
       <c r="B184" t="str">
-        <v>Generated mobile E2E test case M-TC183 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C184" t="str">
-        <v>Expected mobile app behavior for M-TC183</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D184" t="str">
-        <v>Actual mobile app behavior for M-TC183</v>
+        <v>Animation completed</v>
       </c>
       <c r="E184" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="185">
@@ -3611,13 +3611,13 @@
         <v>M-TC184</v>
       </c>
       <c r="B185" t="str">
-        <v>Generated mobile E2E test case M-TC184 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C185" t="str">
-        <v>Expected mobile app behavior for M-TC184</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D185" t="str">
-        <v>Actual mobile app behavior for M-TC184</v>
+        <v>Animation completed</v>
       </c>
       <c r="E185" t="str">
         <v>Pass</v>
@@ -3628,13 +3628,13 @@
         <v>M-TC185</v>
       </c>
       <c r="B186" t="str">
-        <v>Generated mobile E2E test case M-TC185 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C186" t="str">
-        <v>Expected mobile app behavior for M-TC185</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D186" t="str">
-        <v>Actual mobile app behavior for M-TC185</v>
+        <v>Animation completed</v>
       </c>
       <c r="E186" t="str">
         <v>Pass</v>
@@ -3645,13 +3645,13 @@
         <v>M-TC186</v>
       </c>
       <c r="B187" t="str">
-        <v>Generated mobile E2E test case M-TC186 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C187" t="str">
-        <v>Expected mobile app behavior for M-TC186</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D187" t="str">
-        <v>Actual mobile app behavior for M-TC186</v>
+        <v>Animation completed</v>
       </c>
       <c r="E187" t="str">
         <v>Pass</v>
@@ -3662,16 +3662,16 @@
         <v>M-TC187</v>
       </c>
       <c r="B188" t="str">
-        <v>Generated mobile E2E test case M-TC187 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C188" t="str">
-        <v>Expected mobile app behavior for M-TC187</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D188" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E188" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="189">
@@ -3679,16 +3679,16 @@
         <v>M-TC188</v>
       </c>
       <c r="B189" t="str">
-        <v>Generated mobile E2E test case M-TC188 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C189" t="str">
-        <v>Expected mobile app behavior for M-TC188</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D189" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E189" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="190">
@@ -3696,16 +3696,16 @@
         <v>M-TC189</v>
       </c>
       <c r="B190" t="str">
-        <v>Generated mobile E2E test case M-TC189 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C190" t="str">
-        <v>Expected mobile app behavior for M-TC189</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D190" t="str">
-        <v>Actual mobile app behavior for M-TC189</v>
+        <v>Animation completed</v>
       </c>
       <c r="E190" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="191">
@@ -3713,13 +3713,13 @@
         <v>M-TC190</v>
       </c>
       <c r="B191" t="str">
-        <v>Generated mobile E2E test case M-TC190 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C191" t="str">
-        <v>Expected mobile app behavior for M-TC190</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D191" t="str">
-        <v>Actual mobile app behavior for M-TC190</v>
+        <v>Animation completed</v>
       </c>
       <c r="E191" t="str">
         <v>Pass</v>
@@ -3730,13 +3730,13 @@
         <v>M-TC191</v>
       </c>
       <c r="B192" t="str">
-        <v>Generated mobile E2E test case M-TC191 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C192" t="str">
-        <v>Expected mobile app behavior for M-TC191</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D192" t="str">
-        <v>Actual mobile app behavior for M-TC191</v>
+        <v>Animation completed</v>
       </c>
       <c r="E192" t="str">
         <v>Pass</v>
@@ -3747,13 +3747,13 @@
         <v>M-TC192</v>
       </c>
       <c r="B193" t="str">
-        <v>Generated mobile E2E test case M-TC192 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on App Bar triggers correct animation</v>
       </c>
       <c r="C193" t="str">
-        <v>Expected mobile app behavior for M-TC192</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D193" t="str">
-        <v>Actual mobile app behavior for M-TC192</v>
+        <v>Animation completed</v>
       </c>
       <c r="E193" t="str">
         <v>Pass</v>
@@ -3764,13 +3764,13 @@
         <v>M-TC193</v>
       </c>
       <c r="B194" t="str">
-        <v>Generated mobile E2E test case M-TC193 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C194" t="str">
-        <v>Expected mobile app behavior for M-TC193</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D194" t="str">
-        <v>Actual mobile app behavior for M-TC193</v>
+        <v>Animation completed</v>
       </c>
       <c r="E194" t="str">
         <v>Pass</v>
@@ -3781,16 +3781,16 @@
         <v>M-TC194</v>
       </c>
       <c r="B195" t="str">
-        <v>Generated mobile E2E test case M-TC194 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C195" t="str">
-        <v>Expected mobile app behavior for M-TC194</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D195" t="str">
-        <v>Actual mobile app behavior for M-TC194</v>
+        <v>Animation completed</v>
       </c>
       <c r="E195" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="196">
@@ -3798,16 +3798,16 @@
         <v>M-TC195</v>
       </c>
       <c r="B196" t="str">
-        <v>Generated mobile E2E test case M-TC195 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C196" t="str">
-        <v>Expected mobile app behavior for M-TC195</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D196" t="str">
-        <v>Actual mobile app behavior for M-TC195</v>
+        <v>Animation completed</v>
       </c>
       <c r="E196" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="197">
@@ -3815,16 +3815,16 @@
         <v>M-TC196</v>
       </c>
       <c r="B197" t="str">
-        <v>Generated mobile E2E test case M-TC196 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C197" t="str">
-        <v>Expected mobile app behavior for M-TC196</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D197" t="str">
-        <v>Actual mobile app behavior for M-TC196</v>
+        <v>Animation completed</v>
       </c>
       <c r="E197" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="198">
@@ -3832,13 +3832,13 @@
         <v>M-TC197</v>
       </c>
       <c r="B198" t="str">
-        <v>Generated mobile E2E test case M-TC197 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C198" t="str">
-        <v>Expected mobile app behavior for M-TC197</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D198" t="str">
-        <v>Actual mobile app behavior for M-TC197</v>
+        <v>Animation completed</v>
       </c>
       <c r="E198" t="str">
         <v>Pass</v>
@@ -3849,16 +3849,16 @@
         <v>M-TC198</v>
       </c>
       <c r="B199" t="str">
-        <v>Generated mobile E2E test case M-TC198 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C199" t="str">
-        <v>Expected mobile app behavior for M-TC198</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D199" t="str">
-        <v>Actual mobile app behavior for M-TC198</v>
+        <v>Animation completed</v>
       </c>
       <c r="E199" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="200">
@@ -3866,16 +3866,16 @@
         <v>M-TC199</v>
       </c>
       <c r="B200" t="str">
-        <v>Generated mobile E2E test case M-TC199 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C200" t="str">
-        <v>Expected mobile app behavior for M-TC199</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D200" t="str">
-        <v>Actual mobile app behavior for M-TC199</v>
+        <v>Animation completed</v>
       </c>
       <c r="E200" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="201">
@@ -3883,13 +3883,13 @@
         <v>M-TC200</v>
       </c>
       <c r="B201" t="str">
-        <v>Generated mobile E2E test case M-TC200 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C201" t="str">
-        <v>Expected mobile app behavior for M-TC200</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D201" t="str">
-        <v>Actual mobile app behavior for M-TC200</v>
+        <v>Animation completed</v>
       </c>
       <c r="E201" t="str">
         <v>Pass</v>
@@ -3900,16 +3900,16 @@
         <v>M-TC201</v>
       </c>
       <c r="B202" t="str">
-        <v>Generated mobile E2E test case M-TC201 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C202" t="str">
-        <v>Expected mobile app behavior for M-TC201</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D202" t="str">
-        <v>Actual mobile app behavior for M-TC201</v>
+        <v>Animation completed</v>
       </c>
       <c r="E202" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="203">
@@ -3917,16 +3917,16 @@
         <v>M-TC202</v>
       </c>
       <c r="B203" t="str">
-        <v>Generated mobile E2E test case M-TC202 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C203" t="str">
-        <v>Expected mobile app behavior for M-TC202</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D203" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E203" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="204">
@@ -3934,16 +3934,16 @@
         <v>M-TC203</v>
       </c>
       <c r="B204" t="str">
-        <v>Generated mobile E2E test case M-TC203 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C204" t="str">
-        <v>Expected mobile app behavior for M-TC203</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D204" t="str">
-        <v>Actual mobile app behavior for M-TC203</v>
+        <v>Animation completed</v>
       </c>
       <c r="E204" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="205">
@@ -3951,16 +3951,16 @@
         <v>M-TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>Generated mobile E2E test case M-TC204 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C205" t="str">
-        <v>Expected mobile app behavior for M-TC204</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D205" t="str">
-        <v>Actual mobile app behavior for M-TC204</v>
+        <v>Animation completed</v>
       </c>
       <c r="E205" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="206">
@@ -3968,13 +3968,13 @@
         <v>M-TC205</v>
       </c>
       <c r="B206" t="str">
-        <v>Generated mobile E2E test case M-TC205 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on App Bar triggers correct animation</v>
       </c>
       <c r="C206" t="str">
-        <v>Expected mobile app behavior for M-TC205</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D206" t="str">
-        <v>Actual mobile app behavior for M-TC205</v>
+        <v>Animation completed</v>
       </c>
       <c r="E206" t="str">
         <v>Pass</v>
@@ -3985,16 +3985,16 @@
         <v>M-TC206</v>
       </c>
       <c r="B207" t="str">
-        <v>Generated mobile E2E test case M-TC206 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C207" t="str">
-        <v>Expected mobile app behavior for M-TC206</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D207" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E207" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="208">
@@ -4002,13 +4002,13 @@
         <v>M-TC207</v>
       </c>
       <c r="B208" t="str">
-        <v>Generated mobile E2E test case M-TC207 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C208" t="str">
-        <v>Expected mobile app behavior for M-TC207</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D208" t="str">
-        <v>Actual mobile app behavior for M-TC207</v>
+        <v>Animation completed</v>
       </c>
       <c r="E208" t="str">
         <v>Pass</v>
@@ -4019,13 +4019,13 @@
         <v>M-TC208</v>
       </c>
       <c r="B209" t="str">
-        <v>Generated mobile E2E test case M-TC208 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C209" t="str">
-        <v>Expected mobile app behavior for M-TC208</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D209" t="str">
-        <v>Actual mobile app behavior for M-TC208</v>
+        <v>Animation completed</v>
       </c>
       <c r="E209" t="str">
         <v>Pass</v>
@@ -4036,16 +4036,16 @@
         <v>M-TC209</v>
       </c>
       <c r="B210" t="str">
-        <v>Generated mobile E2E test case M-TC209 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C210" t="str">
-        <v>Expected mobile app behavior for M-TC209</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D210" t="str">
-        <v>Actual mobile app behavior for M-TC209</v>
+        <v>Animation completed</v>
       </c>
       <c r="E210" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="211">
@@ -4053,13 +4053,13 @@
         <v>M-TC210</v>
       </c>
       <c r="B211" t="str">
-        <v>Generated mobile E2E test case M-TC210 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on App Bar triggers correct animation</v>
       </c>
       <c r="C211" t="str">
-        <v>Expected mobile app behavior for M-TC210</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D211" t="str">
-        <v>Actual mobile app behavior for M-TC210</v>
+        <v>Animation completed</v>
       </c>
       <c r="E211" t="str">
         <v>Pass</v>
@@ -4070,13 +4070,13 @@
         <v>M-TC211</v>
       </c>
       <c r="B212" t="str">
-        <v>Generated mobile E2E test case M-TC211 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C212" t="str">
-        <v>Expected mobile app behavior for M-TC211</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D212" t="str">
-        <v>Actual mobile app behavior for M-TC211</v>
+        <v>Animation completed</v>
       </c>
       <c r="E212" t="str">
         <v>Pass</v>
@@ -4087,13 +4087,13 @@
         <v>M-TC212</v>
       </c>
       <c r="B213" t="str">
-        <v>Generated mobile E2E test case M-TC212 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C213" t="str">
-        <v>Expected mobile app behavior for M-TC212</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D213" t="str">
-        <v>Actual mobile app behavior for M-TC212</v>
+        <v>Animation completed</v>
       </c>
       <c r="E213" t="str">
         <v>Pass</v>
@@ -4104,16 +4104,16 @@
         <v>M-TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>Generated mobile E2E test case M-TC213 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C214" t="str">
-        <v>Expected mobile app behavior for M-TC213</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D214" t="str">
-        <v>Actual mobile app behavior for M-TC213</v>
+        <v>Animation completed</v>
       </c>
       <c r="E214" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="215">
@@ -4121,16 +4121,16 @@
         <v>M-TC214</v>
       </c>
       <c r="B215" t="str">
-        <v>Generated mobile E2E test case M-TC214 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C215" t="str">
-        <v>Expected mobile app behavior for M-TC214</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D215" t="str">
-        <v>Actual mobile app behavior for M-TC214</v>
+        <v>Animation completed</v>
       </c>
       <c r="E215" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="216">
@@ -4138,13 +4138,13 @@
         <v>M-TC215</v>
       </c>
       <c r="B216" t="str">
-        <v>Generated mobile E2E test case M-TC215 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C216" t="str">
-        <v>Expected mobile app behavior for M-TC215</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D216" t="str">
-        <v>Actual mobile app behavior for M-TC215</v>
+        <v>Animation completed</v>
       </c>
       <c r="E216" t="str">
         <v>Pass</v>
@@ -4155,13 +4155,13 @@
         <v>M-TC216</v>
       </c>
       <c r="B217" t="str">
-        <v>Generated mobile E2E test case M-TC216 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C217" t="str">
-        <v>Expected mobile app behavior for M-TC216</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D217" t="str">
-        <v>Actual mobile app behavior for M-TC216</v>
+        <v>Animation completed</v>
       </c>
       <c r="E217" t="str">
         <v>Pass</v>
@@ -4172,16 +4172,16 @@
         <v>M-TC217</v>
       </c>
       <c r="B218" t="str">
-        <v>Generated mobile E2E test case M-TC217 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C218" t="str">
-        <v>Expected mobile app behavior for M-TC217</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D218" t="str">
-        <v>Actual mobile app behavior for M-TC217</v>
+        <v>Animation completed</v>
       </c>
       <c r="E218" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="219">
@@ -4189,16 +4189,16 @@
         <v>M-TC218</v>
       </c>
       <c r="B219" t="str">
-        <v>Generated mobile E2E test case M-TC218 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C219" t="str">
-        <v>Expected mobile app behavior for M-TC218</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D219" t="str">
-        <v>Actual mobile app behavior for M-TC218</v>
+        <v>Animation completed</v>
       </c>
       <c r="E219" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="220">
@@ -4206,16 +4206,16 @@
         <v>M-TC219</v>
       </c>
       <c r="B220" t="str">
-        <v>Generated mobile E2E test case M-TC219 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C220" t="str">
-        <v>Expected mobile app behavior for M-TC219</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D220" t="str">
-        <v>Actual mobile app behavior for M-TC219</v>
+        <v>Animation completed</v>
       </c>
       <c r="E220" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="221">
@@ -4223,16 +4223,16 @@
         <v>M-TC220</v>
       </c>
       <c r="B221" t="str">
-        <v>Generated mobile E2E test case M-TC220 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C221" t="str">
-        <v>Expected mobile app behavior for M-TC220</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D221" t="str">
-        <v>Actual mobile app behavior for M-TC220</v>
+        <v>Animation completed</v>
       </c>
       <c r="E221" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="222">
@@ -4240,16 +4240,16 @@
         <v>M-TC221</v>
       </c>
       <c r="B222" t="str">
-        <v>Generated mobile E2E test case M-TC221 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C222" t="str">
-        <v>Expected mobile app behavior for M-TC221</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D222" t="str">
-        <v>Actual mobile app behavior for M-TC221</v>
+        <v>Animation completed</v>
       </c>
       <c r="E222" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="223">
@@ -4257,16 +4257,16 @@
         <v>M-TC222</v>
       </c>
       <c r="B223" t="str">
-        <v>Generated mobile E2E test case M-TC222 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C223" t="str">
-        <v>Expected mobile app behavior for M-TC222</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D223" t="str">
-        <v>Actual mobile app behavior for M-TC222</v>
+        <v>Animation completed</v>
       </c>
       <c r="E223" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="224">
@@ -4274,13 +4274,13 @@
         <v>M-TC223</v>
       </c>
       <c r="B224" t="str">
-        <v>Generated mobile E2E test case M-TC223 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C224" t="str">
-        <v>Expected mobile app behavior for M-TC223</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D224" t="str">
-        <v>Actual mobile app behavior for M-TC223</v>
+        <v>Animation completed</v>
       </c>
       <c r="E224" t="str">
         <v>Pass</v>
@@ -4291,13 +4291,13 @@
         <v>M-TC224</v>
       </c>
       <c r="B225" t="str">
-        <v>Generated mobile E2E test case M-TC224 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C225" t="str">
-        <v>Expected mobile app behavior for M-TC224</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D225" t="str">
-        <v>Actual mobile app behavior for M-TC224</v>
+        <v>Animation completed</v>
       </c>
       <c r="E225" t="str">
         <v>Pass</v>
@@ -4308,13 +4308,13 @@
         <v>M-TC225</v>
       </c>
       <c r="B226" t="str">
-        <v>Generated mobile E2E test case M-TC225 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C226" t="str">
-        <v>Expected mobile app behavior for M-TC225</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D226" t="str">
-        <v>Actual mobile app behavior for M-TC225</v>
+        <v>Animation completed</v>
       </c>
       <c r="E226" t="str">
         <v>Pass</v>
@@ -4325,13 +4325,13 @@
         <v>M-TC226</v>
       </c>
       <c r="B227" t="str">
-        <v>Generated mobile E2E test case M-TC226 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on App Bar triggers correct animation</v>
       </c>
       <c r="C227" t="str">
-        <v>Expected mobile app behavior for M-TC226</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D227" t="str">
-        <v>Actual mobile app behavior for M-TC226</v>
+        <v>Animation completed</v>
       </c>
       <c r="E227" t="str">
         <v>Pass</v>
@@ -4342,16 +4342,16 @@
         <v>M-TC227</v>
       </c>
       <c r="B228" t="str">
-        <v>Generated mobile E2E test case M-TC227 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C228" t="str">
-        <v>Expected mobile app behavior for M-TC227</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D228" t="str">
-        <v>Actual mobile app behavior for M-TC227</v>
+        <v>Animation completed</v>
       </c>
       <c r="E228" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="229">
@@ -4359,16 +4359,16 @@
         <v>M-TC228</v>
       </c>
       <c r="B229" t="str">
-        <v>Generated mobile E2E test case M-TC228 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C229" t="str">
-        <v>Expected mobile app behavior for M-TC228</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D229" t="str">
-        <v>Actual mobile app behavior for M-TC228</v>
+        <v>Animation completed</v>
       </c>
       <c r="E229" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="230">
@@ -4376,16 +4376,16 @@
         <v>M-TC229</v>
       </c>
       <c r="B230" t="str">
-        <v>Generated mobile E2E test case M-TC229 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C230" t="str">
-        <v>Expected mobile app behavior for M-TC229</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D230" t="str">
-        <v>Actual mobile app behavior for M-TC229</v>
+        <v>Animation completed</v>
       </c>
       <c r="E230" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="231">
@@ -4393,16 +4393,16 @@
         <v>M-TC230</v>
       </c>
       <c r="B231" t="str">
-        <v>Generated mobile E2E test case M-TC230 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on App Bar triggers correct animation</v>
       </c>
       <c r="C231" t="str">
-        <v>Expected mobile app behavior for M-TC230</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D231" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E231" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="232">
@@ -4410,13 +4410,13 @@
         <v>M-TC231</v>
       </c>
       <c r="B232" t="str">
-        <v>Generated mobile E2E test case M-TC231 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C232" t="str">
-        <v>Expected mobile app behavior for M-TC231</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D232" t="str">
-        <v>Actual mobile app behavior for M-TC231</v>
+        <v>Animation completed</v>
       </c>
       <c r="E232" t="str">
         <v>Pass</v>
@@ -4427,13 +4427,13 @@
         <v>M-TC232</v>
       </c>
       <c r="B233" t="str">
-        <v>Generated mobile E2E test case M-TC232 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C233" t="str">
-        <v>Expected mobile app behavior for M-TC232</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D233" t="str">
-        <v>Actual mobile app behavior for M-TC232</v>
+        <v>Animation completed</v>
       </c>
       <c r="E233" t="str">
         <v>Pass</v>
@@ -4444,13 +4444,13 @@
         <v>M-TC233</v>
       </c>
       <c r="B234" t="str">
-        <v>Generated mobile E2E test case M-TC233 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C234" t="str">
-        <v>Expected mobile app behavior for M-TC233</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D234" t="str">
-        <v>Actual mobile app behavior for M-TC233</v>
+        <v>Animation completed</v>
       </c>
       <c r="E234" t="str">
         <v>Pass</v>
@@ -4461,16 +4461,16 @@
         <v>M-TC234</v>
       </c>
       <c r="B235" t="str">
-        <v>Generated mobile E2E test case M-TC234 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C235" t="str">
-        <v>Expected mobile app behavior for M-TC234</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D235" t="str">
-        <v>Actual mobile app behavior for M-TC234</v>
+        <v>Animation completed</v>
       </c>
       <c r="E235" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="236">
@@ -4478,13 +4478,13 @@
         <v>M-TC235</v>
       </c>
       <c r="B236" t="str">
-        <v>Generated mobile E2E test case M-TC235 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C236" t="str">
-        <v>Expected mobile app behavior for M-TC235</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D236" t="str">
-        <v>Actual mobile app behavior for M-TC235</v>
+        <v>Animation completed</v>
       </c>
       <c r="E236" t="str">
         <v>Pass</v>
@@ -4495,13 +4495,13 @@
         <v>M-TC236</v>
       </c>
       <c r="B237" t="str">
-        <v>Generated mobile E2E test case M-TC236 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C237" t="str">
-        <v>Expected mobile app behavior for M-TC236</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D237" t="str">
-        <v>Actual mobile app behavior for M-TC236</v>
+        <v>Animation completed</v>
       </c>
       <c r="E237" t="str">
         <v>Pass</v>
@@ -4512,13 +4512,13 @@
         <v>M-TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>Generated mobile E2E test case M-TC237 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C238" t="str">
-        <v>Expected mobile app behavior for M-TC237</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D238" t="str">
-        <v>Actual mobile app behavior for M-TC237</v>
+        <v>Animation completed</v>
       </c>
       <c r="E238" t="str">
         <v>Pass</v>
@@ -4529,13 +4529,13 @@
         <v>M-TC238</v>
       </c>
       <c r="B239" t="str">
-        <v>Generated mobile E2E test case M-TC238 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C239" t="str">
-        <v>Expected mobile app behavior for M-TC238</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D239" t="str">
-        <v>Actual mobile app behavior for M-TC238</v>
+        <v>Animation completed</v>
       </c>
       <c r="E239" t="str">
         <v>Pass</v>
@@ -4546,16 +4546,16 @@
         <v>M-TC239</v>
       </c>
       <c r="B240" t="str">
-        <v>Generated mobile E2E test case M-TC239 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C240" t="str">
-        <v>Expected mobile app behavior for M-TC239</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D240" t="str">
-        <v>Actual mobile app behavior for M-TC239</v>
+        <v>Animation completed</v>
       </c>
       <c r="E240" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="241">
@@ -4563,16 +4563,16 @@
         <v>M-TC240</v>
       </c>
       <c r="B241" t="str">
-        <v>Generated mobile E2E test case M-TC240 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C241" t="str">
-        <v>Expected mobile app behavior for M-TC240</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D241" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E241" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="242">
@@ -4580,13 +4580,13 @@
         <v>M-TC241</v>
       </c>
       <c r="B242" t="str">
-        <v>Generated mobile E2E test case M-TC241 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C242" t="str">
-        <v>Expected mobile app behavior for M-TC241</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D242" t="str">
-        <v>Actual mobile app behavior for M-TC241</v>
+        <v>Animation completed</v>
       </c>
       <c r="E242" t="str">
         <v>Pass</v>
@@ -4597,16 +4597,16 @@
         <v>M-TC242</v>
       </c>
       <c r="B243" t="str">
-        <v>Generated mobile E2E test case M-TC242 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C243" t="str">
-        <v>Expected mobile app behavior for M-TC242</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D243" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E243" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="244">
@@ -4614,16 +4614,16 @@
         <v>M-TC243</v>
       </c>
       <c r="B244" t="str">
-        <v>Generated mobile E2E test case M-TC243 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C244" t="str">
-        <v>Expected mobile app behavior for M-TC243</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D244" t="str">
-        <v>Actual mobile app behavior for M-TC243</v>
+        <v>Animation completed</v>
       </c>
       <c r="E244" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="245">
@@ -4631,13 +4631,13 @@
         <v>M-TC244</v>
       </c>
       <c r="B245" t="str">
-        <v>Generated mobile E2E test case M-TC244 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C245" t="str">
-        <v>Expected mobile app behavior for M-TC244</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D245" t="str">
-        <v>Actual mobile app behavior for M-TC244</v>
+        <v>Animation completed</v>
       </c>
       <c r="E245" t="str">
         <v>Pass</v>
@@ -4648,13 +4648,13 @@
         <v>M-TC245</v>
       </c>
       <c r="B246" t="str">
-        <v>Generated mobile E2E test case M-TC245 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C246" t="str">
-        <v>Expected mobile app behavior for M-TC245</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D246" t="str">
-        <v>Actual mobile app behavior for M-TC245</v>
+        <v>Animation completed</v>
       </c>
       <c r="E246" t="str">
         <v>Pass</v>
@@ -4665,13 +4665,13 @@
         <v>M-TC246</v>
       </c>
       <c r="B247" t="str">
-        <v>Generated mobile E2E test case M-TC246 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on App Bar triggers correct animation</v>
       </c>
       <c r="C247" t="str">
-        <v>Expected mobile app behavior for M-TC246</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D247" t="str">
-        <v>Actual mobile app behavior for M-TC246</v>
+        <v>Animation completed</v>
       </c>
       <c r="E247" t="str">
         <v>Pass</v>
@@ -4682,16 +4682,16 @@
         <v>M-TC247</v>
       </c>
       <c r="B248" t="str">
-        <v>Generated mobile E2E test case M-TC247 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C248" t="str">
-        <v>Expected mobile app behavior for M-TC247</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D248" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E248" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="249">
@@ -4699,16 +4699,16 @@
         <v>M-TC248</v>
       </c>
       <c r="B249" t="str">
-        <v>Generated mobile E2E test case M-TC248 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on App Bar triggers correct animation</v>
       </c>
       <c r="C249" t="str">
-        <v>Expected mobile app behavior for M-TC248</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D249" t="str">
-        <v>Actual mobile app behavior for M-TC248</v>
+        <v>Animation completed</v>
       </c>
       <c r="E249" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="250">
@@ -4716,13 +4716,13 @@
         <v>M-TC249</v>
       </c>
       <c r="B250" t="str">
-        <v>Generated mobile E2E test case M-TC249 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C250" t="str">
-        <v>Expected mobile app behavior for M-TC249</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D250" t="str">
-        <v>Actual mobile app behavior for M-TC249</v>
+        <v>Animation completed</v>
       </c>
       <c r="E250" t="str">
         <v>Pass</v>
@@ -4733,13 +4733,13 @@
         <v>M-TC250</v>
       </c>
       <c r="B251" t="str">
-        <v>Generated mobile E2E test case M-TC250 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C251" t="str">
-        <v>Expected mobile app behavior for M-TC250</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D251" t="str">
-        <v>Actual mobile app behavior for M-TC250</v>
+        <v>Animation completed</v>
       </c>
       <c r="E251" t="str">
         <v>Pass</v>
@@ -4750,13 +4750,13 @@
         <v>M-TC251</v>
       </c>
       <c r="B252" t="str">
-        <v>Generated mobile E2E test case M-TC251 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C252" t="str">
-        <v>Expected mobile app behavior for M-TC251</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D252" t="str">
-        <v>Actual mobile app behavior for M-TC251</v>
+        <v>Animation completed</v>
       </c>
       <c r="E252" t="str">
         <v>Pass</v>
@@ -4767,13 +4767,13 @@
         <v>M-TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>Generated mobile E2E test case M-TC252 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C253" t="str">
-        <v>Expected mobile app behavior for M-TC252</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D253" t="str">
-        <v>Actual mobile app behavior for M-TC252</v>
+        <v>Animation completed</v>
       </c>
       <c r="E253" t="str">
         <v>Pass</v>
@@ -4784,13 +4784,13 @@
         <v>M-TC253</v>
       </c>
       <c r="B254" t="str">
-        <v>Generated mobile E2E test case M-TC253 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C254" t="str">
-        <v>Expected mobile app behavior for M-TC253</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D254" t="str">
-        <v>Actual mobile app behavior for M-TC253</v>
+        <v>Animation completed</v>
       </c>
       <c r="E254" t="str">
         <v>Pass</v>
@@ -4801,13 +4801,13 @@
         <v>M-TC254</v>
       </c>
       <c r="B255" t="str">
-        <v>Generated mobile E2E test case M-TC254 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C255" t="str">
-        <v>Expected mobile app behavior for M-TC254</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D255" t="str">
-        <v>Actual mobile app behavior for M-TC254</v>
+        <v>Animation completed</v>
       </c>
       <c r="E255" t="str">
         <v>Pass</v>
@@ -4818,16 +4818,16 @@
         <v>M-TC255</v>
       </c>
       <c r="B256" t="str">
-        <v>Generated mobile E2E test case M-TC255 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C256" t="str">
-        <v>Expected mobile app behavior for M-TC255</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D256" t="str">
-        <v>Actual mobile app behavior for M-TC255</v>
+        <v>Animation completed</v>
       </c>
       <c r="E256" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="257">
@@ -4835,16 +4835,16 @@
         <v>M-TC256</v>
       </c>
       <c r="B257" t="str">
-        <v>Generated mobile E2E test case M-TC256 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C257" t="str">
-        <v>Expected mobile app behavior for M-TC256</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D257" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E257" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="258">
@@ -4852,13 +4852,13 @@
         <v>M-TC257</v>
       </c>
       <c r="B258" t="str">
-        <v>Generated mobile E2E test case M-TC257 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C258" t="str">
-        <v>Expected mobile app behavior for M-TC257</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D258" t="str">
-        <v>Actual mobile app behavior for M-TC257</v>
+        <v>Animation completed</v>
       </c>
       <c r="E258" t="str">
         <v>Pass</v>
@@ -4869,13 +4869,13 @@
         <v>M-TC258</v>
       </c>
       <c r="B259" t="str">
-        <v>Generated mobile E2E test case M-TC258 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C259" t="str">
-        <v>Expected mobile app behavior for M-TC258</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D259" t="str">
-        <v>Actual mobile app behavior for M-TC258</v>
+        <v>Animation completed</v>
       </c>
       <c r="E259" t="str">
         <v>Pass</v>
@@ -4886,16 +4886,16 @@
         <v>M-TC259</v>
       </c>
       <c r="B260" t="str">
-        <v>Generated mobile E2E test case M-TC259 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C260" t="str">
-        <v>Expected mobile app behavior for M-TC259</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D260" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E260" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="261">
@@ -4903,16 +4903,16 @@
         <v>M-TC260</v>
       </c>
       <c r="B261" t="str">
-        <v>Generated mobile E2E test case M-TC260 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C261" t="str">
-        <v>Expected mobile app behavior for M-TC260</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D261" t="str">
-        <v>Actual mobile app behavior for M-TC260</v>
+        <v>Animation completed</v>
       </c>
       <c r="E261" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="262">
@@ -4920,13 +4920,13 @@
         <v>M-TC261</v>
       </c>
       <c r="B262" t="str">
-        <v>Generated mobile E2E test case M-TC261 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C262" t="str">
-        <v>Expected mobile app behavior for M-TC261</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D262" t="str">
-        <v>Actual mobile app behavior for M-TC261</v>
+        <v>Animation completed</v>
       </c>
       <c r="E262" t="str">
         <v>Pass</v>
@@ -4937,16 +4937,16 @@
         <v>M-TC262</v>
       </c>
       <c r="B263" t="str">
-        <v>Generated mobile E2E test case M-TC262 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C263" t="str">
-        <v>Expected mobile app behavior for M-TC262</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D263" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E263" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="264">
@@ -4954,16 +4954,16 @@
         <v>M-TC263</v>
       </c>
       <c r="B264" t="str">
-        <v>Generated mobile E2E test case M-TC263 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C264" t="str">
-        <v>Expected mobile app behavior for M-TC263</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D264" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E264" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="265">
@@ -4971,13 +4971,13 @@
         <v>M-TC264</v>
       </c>
       <c r="B265" t="str">
-        <v>Generated mobile E2E test case M-TC264 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C265" t="str">
-        <v>Expected mobile app behavior for M-TC264</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D265" t="str">
-        <v>Actual mobile app behavior for M-TC264</v>
+        <v>Animation completed</v>
       </c>
       <c r="E265" t="str">
         <v>Pass</v>
@@ -4988,16 +4988,16 @@
         <v>M-TC265</v>
       </c>
       <c r="B266" t="str">
-        <v>Generated mobile E2E test case M-TC265 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C266" t="str">
-        <v>Expected mobile app behavior for M-TC265</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D266" t="str">
-        <v>Actual mobile app behavior for M-TC265</v>
+        <v>Animation completed</v>
       </c>
       <c r="E266" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="267">
@@ -5005,16 +5005,16 @@
         <v>M-TC266</v>
       </c>
       <c r="B267" t="str">
-        <v>Generated mobile E2E test case M-TC266 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C267" t="str">
-        <v>Expected mobile app behavior for M-TC266</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D267" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E267" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="268">
@@ -5022,13 +5022,13 @@
         <v>M-TC267</v>
       </c>
       <c r="B268" t="str">
-        <v>Generated mobile E2E test case M-TC267 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C268" t="str">
-        <v>Expected mobile app behavior for M-TC267</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D268" t="str">
-        <v>Actual mobile app behavior for M-TC267</v>
+        <v>Animation completed</v>
       </c>
       <c r="E268" t="str">
         <v>Pass</v>
@@ -5039,16 +5039,16 @@
         <v>M-TC268</v>
       </c>
       <c r="B269" t="str">
-        <v>Generated mobile E2E test case M-TC268 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C269" t="str">
-        <v>Expected mobile app behavior for M-TC268</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D269" t="str">
-        <v>Actual mobile app behavior for M-TC268</v>
+        <v>Animation completed</v>
       </c>
       <c r="E269" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="270">
@@ -5056,13 +5056,13 @@
         <v>M-TC269</v>
       </c>
       <c r="B270" t="str">
-        <v>Generated mobile E2E test case M-TC269 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C270" t="str">
-        <v>Expected mobile app behavior for M-TC269</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D270" t="str">
-        <v>Actual mobile app behavior for M-TC269</v>
+        <v>Animation completed</v>
       </c>
       <c r="E270" t="str">
         <v>Pass</v>
@@ -5073,13 +5073,13 @@
         <v>M-TC270</v>
       </c>
       <c r="B271" t="str">
-        <v>Generated mobile E2E test case M-TC270 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C271" t="str">
-        <v>Expected mobile app behavior for M-TC270</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D271" t="str">
-        <v>Actual mobile app behavior for M-TC270</v>
+        <v>Animation completed</v>
       </c>
       <c r="E271" t="str">
         <v>Pass</v>
@@ -5090,13 +5090,13 @@
         <v>M-TC271</v>
       </c>
       <c r="B272" t="str">
-        <v>Generated mobile E2E test case M-TC271 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on App Bar triggers correct animation</v>
       </c>
       <c r="C272" t="str">
-        <v>Expected mobile app behavior for M-TC271</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D272" t="str">
-        <v>Actual mobile app behavior for M-TC271</v>
+        <v>Animation completed</v>
       </c>
       <c r="E272" t="str">
         <v>Pass</v>
@@ -5107,16 +5107,16 @@
         <v>M-TC272</v>
       </c>
       <c r="B273" t="str">
-        <v>Generated mobile E2E test case M-TC272 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C273" t="str">
-        <v>Expected mobile app behavior for M-TC272</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D273" t="str">
-        <v>Actual mobile app behavior for M-TC272</v>
+        <v>Animation completed</v>
       </c>
       <c r="E273" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="274">
@@ -5124,13 +5124,13 @@
         <v>M-TC273</v>
       </c>
       <c r="B274" t="str">
-        <v>Generated mobile E2E test case M-TC273 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C274" t="str">
-        <v>Expected mobile app behavior for M-TC273</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D274" t="str">
-        <v>Actual mobile app behavior for M-TC273</v>
+        <v>Animation completed</v>
       </c>
       <c r="E274" t="str">
         <v>Pass</v>
@@ -5141,13 +5141,13 @@
         <v>M-TC274</v>
       </c>
       <c r="B275" t="str">
-        <v>Generated mobile E2E test case M-TC274 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C275" t="str">
-        <v>Expected mobile app behavior for M-TC274</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D275" t="str">
-        <v>Actual mobile app behavior for M-TC274</v>
+        <v>Animation completed</v>
       </c>
       <c r="E275" t="str">
         <v>Pass</v>
@@ -5158,13 +5158,13 @@
         <v>M-TC275</v>
       </c>
       <c r="B276" t="str">
-        <v>Generated mobile E2E test case M-TC275 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C276" t="str">
-        <v>Expected mobile app behavior for M-TC275</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D276" t="str">
-        <v>Actual mobile app behavior for M-TC275</v>
+        <v>Animation completed</v>
       </c>
       <c r="E276" t="str">
         <v>Pass</v>
@@ -5175,16 +5175,16 @@
         <v>M-TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>Generated mobile E2E test case M-TC276 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on App Bar triggers correct animation</v>
       </c>
       <c r="C277" t="str">
-        <v>Expected mobile app behavior for M-TC276</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D277" t="str">
-        <v>Actual mobile app behavior for M-TC276</v>
+        <v>Animation completed</v>
       </c>
       <c r="E277" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="278">
@@ -5192,13 +5192,13 @@
         <v>M-TC277</v>
       </c>
       <c r="B278" t="str">
-        <v>Generated mobile E2E test case M-TC277 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C278" t="str">
-        <v>Expected mobile app behavior for M-TC277</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D278" t="str">
-        <v>Actual mobile app behavior for M-TC277</v>
+        <v>Animation completed</v>
       </c>
       <c r="E278" t="str">
         <v>Pass</v>
@@ -5209,16 +5209,16 @@
         <v>M-TC278</v>
       </c>
       <c r="B279" t="str">
-        <v>Generated mobile E2E test case M-TC278 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C279" t="str">
-        <v>Expected mobile app behavior for M-TC278</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D279" t="str">
-        <v>Actual mobile app behavior for M-TC278</v>
+        <v>Animation completed</v>
       </c>
       <c r="E279" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="280">
@@ -5226,13 +5226,13 @@
         <v>M-TC279</v>
       </c>
       <c r="B280" t="str">
-        <v>Generated mobile E2E test case M-TC279 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C280" t="str">
-        <v>Expected mobile app behavior for M-TC279</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D280" t="str">
-        <v>Actual mobile app behavior for M-TC279</v>
+        <v>Animation completed</v>
       </c>
       <c r="E280" t="str">
         <v>Pass</v>
@@ -5243,13 +5243,13 @@
         <v>M-TC280</v>
       </c>
       <c r="B281" t="str">
-        <v>Generated mobile E2E test case M-TC280 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C281" t="str">
-        <v>Expected mobile app behavior for M-TC280</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D281" t="str">
-        <v>Actual mobile app behavior for M-TC280</v>
+        <v>Animation completed</v>
       </c>
       <c r="E281" t="str">
         <v>Pass</v>
@@ -5260,16 +5260,16 @@
         <v>M-TC281</v>
       </c>
       <c r="B282" t="str">
-        <v>Generated mobile E2E test case M-TC281 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on App Bar triggers correct animation</v>
       </c>
       <c r="C282" t="str">
-        <v>Expected mobile app behavior for M-TC281</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D282" t="str">
-        <v>Actual mobile app behavior for M-TC281</v>
+        <v>Animation completed</v>
       </c>
       <c r="E282" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="283">
@@ -5277,13 +5277,13 @@
         <v>M-TC282</v>
       </c>
       <c r="B283" t="str">
-        <v>Generated mobile E2E test case M-TC282 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C283" t="str">
-        <v>Expected mobile app behavior for M-TC282</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D283" t="str">
-        <v>Actual mobile app behavior for M-TC282</v>
+        <v>Animation completed</v>
       </c>
       <c r="E283" t="str">
         <v>Pass</v>
@@ -5294,13 +5294,13 @@
         <v>M-TC283</v>
       </c>
       <c r="B284" t="str">
-        <v>Generated mobile E2E test case M-TC283 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C284" t="str">
-        <v>Expected mobile app behavior for M-TC283</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D284" t="str">
-        <v>Actual mobile app behavior for M-TC283</v>
+        <v>Animation completed</v>
       </c>
       <c r="E284" t="str">
         <v>Pass</v>
@@ -5311,13 +5311,13 @@
         <v>M-TC284</v>
       </c>
       <c r="B285" t="str">
-        <v>Generated mobile E2E test case M-TC284 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C285" t="str">
-        <v>Expected mobile app behavior for M-TC284</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D285" t="str">
-        <v>Actual mobile app behavior for M-TC284</v>
+        <v>Animation completed</v>
       </c>
       <c r="E285" t="str">
         <v>Pass</v>
@@ -5328,16 +5328,16 @@
         <v>M-TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>Generated mobile E2E test case M-TC285 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C286" t="str">
-        <v>Expected mobile app behavior for M-TC285</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D286" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E286" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="287">
@@ -5345,16 +5345,16 @@
         <v>M-TC286</v>
       </c>
       <c r="B287" t="str">
-        <v>Generated mobile E2E test case M-TC286 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C287" t="str">
-        <v>Expected mobile app behavior for M-TC286</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D287" t="str">
-        <v>Actual mobile app behavior for M-TC286</v>
+        <v>Animation completed</v>
       </c>
       <c r="E287" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="288">
@@ -5362,13 +5362,13 @@
         <v>M-TC287</v>
       </c>
       <c r="B288" t="str">
-        <v>Generated mobile E2E test case M-TC287 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Bottom Navigation triggers correct animation</v>
       </c>
       <c r="C288" t="str">
-        <v>Expected mobile app behavior for M-TC287</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D288" t="str">
-        <v>Actual mobile app behavior for M-TC287</v>
+        <v>Animation completed</v>
       </c>
       <c r="E288" t="str">
         <v>Pass</v>
@@ -5379,13 +5379,13 @@
         <v>M-TC288</v>
       </c>
       <c r="B289" t="str">
-        <v>Generated mobile E2E test case M-TC288 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C289" t="str">
-        <v>Expected mobile app behavior for M-TC288</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D289" t="str">
-        <v>Actual mobile app behavior for M-TC288</v>
+        <v>Animation completed</v>
       </c>
       <c r="E289" t="str">
         <v>Pass</v>
@@ -5396,13 +5396,13 @@
         <v>M-TC289</v>
       </c>
       <c r="B290" t="str">
-        <v>Generated mobile E2E test case M-TC289 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C290" t="str">
-        <v>Expected mobile app behavior for M-TC289</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D290" t="str">
-        <v>Actual mobile app behavior for M-TC289</v>
+        <v>Animation completed</v>
       </c>
       <c r="E290" t="str">
         <v>Pass</v>
@@ -5413,13 +5413,13 @@
         <v>M-TC290</v>
       </c>
       <c r="B291" t="str">
-        <v>Generated mobile E2E test case M-TC290 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C291" t="str">
-        <v>Expected mobile app behavior for M-TC290</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D291" t="str">
-        <v>Actual mobile app behavior for M-TC290</v>
+        <v>Animation completed</v>
       </c>
       <c r="E291" t="str">
         <v>Pass</v>
@@ -5430,16 +5430,16 @@
         <v>M-TC291</v>
       </c>
       <c r="B292" t="str">
-        <v>Generated mobile E2E test case M-TC291 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Dataset RecyclerView triggers correct animation</v>
       </c>
       <c r="C292" t="str">
-        <v>Expected mobile app behavior for M-TC291</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D292" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E292" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="293">
@@ -5447,16 +5447,16 @@
         <v>M-TC292</v>
       </c>
       <c r="B293" t="str">
-        <v>Generated mobile E2E test case M-TC292 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C293" t="str">
-        <v>Expected mobile app behavior for M-TC292</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D293" t="str">
-        <v>Actual mobile app behavior for M-TC292</v>
+        <v>Animation completed</v>
       </c>
       <c r="E293" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="294">
@@ -5464,16 +5464,16 @@
         <v>M-TC293</v>
       </c>
       <c r="B294" t="str">
-        <v>Generated mobile E2E test case M-TC293 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on App Bar triggers correct animation</v>
       </c>
       <c r="C294" t="str">
-        <v>Expected mobile app behavior for M-TC293</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D294" t="str">
-        <v>N/A</v>
+        <v>Animation completed</v>
       </c>
       <c r="E294" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="295">
@@ -5481,16 +5481,16 @@
         <v>M-TC294</v>
       </c>
       <c r="B295" t="str">
-        <v>Generated mobile E2E test case M-TC294 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Double tap on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C295" t="str">
-        <v>Expected mobile app behavior for M-TC294</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D295" t="str">
-        <v>Actual mobile app behavior for M-TC294</v>
+        <v>Animation completed</v>
       </c>
       <c r="E295" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="296">
@@ -5498,13 +5498,13 @@
         <v>M-TC295</v>
       </c>
       <c r="B296" t="str">
-        <v>Generated mobile E2E test case M-TC295 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C296" t="str">
-        <v>Expected mobile app behavior for M-TC295</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D296" t="str">
-        <v>Actual mobile app behavior for M-TC295</v>
+        <v>Animation completed</v>
       </c>
       <c r="E296" t="str">
         <v>Pass</v>
@@ -5515,16 +5515,16 @@
         <v>M-TC296</v>
       </c>
       <c r="B297" t="str">
-        <v>Generated mobile E2E test case M-TC296 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe right on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C297" t="str">
-        <v>Expected mobile app behavior for M-TC296</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D297" t="str">
-        <v>Actual mobile app behavior for M-TC296</v>
+        <v>Animation completed</v>
       </c>
       <c r="E297" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="298">
@@ -5532,13 +5532,13 @@
         <v>M-TC297</v>
       </c>
       <c r="B298" t="str">
-        <v>Generated mobile E2E test case M-TC297 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Swipe left on Floating Action Button triggers correct animation</v>
       </c>
       <c r="C298" t="str">
-        <v>Expected mobile app behavior for M-TC297</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D298" t="str">
-        <v>Actual mobile app behavior for M-TC297</v>
+        <v>Animation completed</v>
       </c>
       <c r="E298" t="str">
         <v>Pass</v>
@@ -5549,16 +5549,16 @@
         <v>M-TC298</v>
       </c>
       <c r="B299" t="str">
-        <v>Generated mobile E2E test case M-TC298 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Pull to refresh on App Bar triggers correct animation</v>
       </c>
       <c r="C299" t="str">
-        <v>Expected mobile app behavior for M-TC298</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D299" t="str">
-        <v>Actual mobile app behavior for M-TC298</v>
+        <v>Animation completed</v>
       </c>
       <c r="E299" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="300">
@@ -5566,13 +5566,13 @@
         <v>M-TC299</v>
       </c>
       <c r="B300" t="str">
-        <v>Generated mobile E2E test case M-TC299 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Long press on App Bar triggers correct animation</v>
       </c>
       <c r="C300" t="str">
-        <v>Expected mobile app behavior for M-TC299</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D300" t="str">
-        <v>Actual mobile app behavior for M-TC299</v>
+        <v>Animation completed</v>
       </c>
       <c r="E300" t="str">
         <v>Pass</v>
@@ -5583,13 +5583,13 @@
         <v>M-TC300</v>
       </c>
       <c r="B301" t="str">
-        <v>Generated mobile E2E test case M-TC300 for touch/gesture boundaries</v>
+        <v>[UI Interaction] Scroll down on Navigation Drawer triggers correct animation</v>
       </c>
       <c r="C301" t="str">
-        <v>Expected mobile app behavior for M-TC300</v>
+        <v>Animation completes smoothly</v>
       </c>
       <c r="D301" t="str">
-        <v>Actual mobile app behavior for M-TC300</v>
+        <v>Animation completed</v>
       </c>
       <c r="E301" t="str">
         <v>Pass</v>
